--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R008497c5208e4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R74f71c7bc90343eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R54da616b5d064840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R882c2d6af3f54159"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rb526e06c9dd345a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd2177746abfe4a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rc0f9b47166774fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ree80284d7f634f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R9c9682b0531f461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rb5417d9c192f465d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T8_0" displayName="T8_0" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T8_0" displayName="T8_0" ref="A1:K11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T8_1" displayName="T8_1" ref="A1:S23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T8_1" displayName="T8_1" ref="A1:S48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T8_2" displayName="T8_2" ref="A1:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T8_2" displayName="T8_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T8_3" displayName="T8_3" ref="A1:L16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T8_3" displayName="T8_3" ref="A1:L31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T8_4" displayName="T8_4" ref="A1:G18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T8_4" displayName="T8_4" ref="A1:G44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -647,10 +647,175 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>本硕博分别开始结束年月未披露；1995-09至2005-03只作为合并教育区间保存，授位年份单独有明确作者简介支持。；本人各阶段直接导师及博士后合作导师未获明确证据；合著者毛志刚、Mingoo Seok等不自动认定师承。；三个职称各自晋升年月与现行校区未确认。</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>入学、离校年月与导师未由已核第一方材料确认；不推定硕士学位或本科四年制起始年。；学术正文英文electronic engineering按原词保留，不自动等同具体中国学科代码。；公开当前名录没有任职开始年月；未采用同名政治、医学、土木人物记录。</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>三个学历阶段开始结束时间未确认，2010-06仅博士论文封面提交时间。；本科和硕士导师未获直接证据；Dr. Wei普通支持性致谢不构成第二导师。；英文Zhigang Ji存在其他学科同名作者，未合并科学史等人物；身份依据微电子领域、学位和上海交大作者任职。；当前任职起始年月、退休状态及校区未确认。</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>本科、硕士、博士及博士后直接导师暂缺满足本项目口径的明确师承语句或正式论文advisor字段；合著与实验室毕业名单不升级师承。；授位月未明确，保留年份；不把清华博士后当作第四学位。</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>三个学位的学习起止与授位年月均未披露；本科专业未知。；本人各阶段直接导师及访问合作导师未确认；不从同事、论文作者或他人论文致谢推断。；本人任职开始年月和校区未确认。</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e1dd6fc809349aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93a5ee5e9404537"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1681,10 +1846,1183 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str"/>
+      <x:c r="F24" s="6" t="str"/>
+      <x:c r="G24" s="6" t="str">
+        <x:v>微电子学与固体电子学</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L24" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="str">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="N24" s="6" t="str"/>
+      <x:c r="O24" s="6" t="str">
+        <x:v>作者简介明确分别获得三学位年份；官网1995-09至2005-03是完整本硕博跨度，未披露各阶段全部边界，不按年限推断。</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q24" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="R24" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S24" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str"/>
+      <x:c r="G25" s="6" t="str">
+        <x:v>微电子学与固体电子学</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L25" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="str">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="N25" s="6" t="str"/>
+      <x:c r="O25" s="6" t="str">
+        <x:v>作者简介明确分别获得三学位年份；官网1995-09至2005-03是完整本硕博跨度，未披露各阶段全部边界，不按年限推断。</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q25" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="R25" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S25" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str"/>
+      <x:c r="F26" s="6" t="str"/>
+      <x:c r="G26" s="6" t="str">
+        <x:v>微电子学与固体电子学</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J26" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L26" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M26" s="7" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="N26" s="6" t="str"/>
+      <x:c r="O26" s="6" t="str">
+        <x:v>作者简介明确分别获得三学位年份；官网1995-09至2005-03是完整本硕博跨度，未披露各阶段全部边界，不按年限推断。</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q26" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="R26" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S26" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str"/>
+      <x:c r="F27" s="6" t="str"/>
+      <x:c r="G27" s="6" t="str"/>
+      <x:c r="H27" s="6" t="str"/>
+      <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str"/>
+      <x:c r="K27" s="6" t="str"/>
+      <x:c r="L27" s="6" t="str"/>
+      <x:c r="M27" s="7" t="str"/>
+      <x:c r="N27" s="6" t="str"/>
+      <x:c r="O27" s="6" t="str">
+        <x:v>现行官方名录列示，不代表独立人事在岗核验；起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P27" s="6" t="str"/>
+      <x:c r="Q27" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="R27" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S27" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>博士后研究员</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>香港科技大学电子与计算机工程系</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str"/>
+      <x:c r="H28" s="6" t="str"/>
+      <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str"/>
+      <x:c r="K28" s="6" t="str"/>
+      <x:c r="L28" s="6" t="str"/>
+      <x:c r="M28" s="7" t="str"/>
+      <x:c r="N28" s="6" t="str"/>
+      <x:c r="O28" s="6" t="str">
+        <x:v>非授位经历；合作导师未公开确认。</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="str"/>
+      <x:c r="Q28" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/heweifeng/zh_CN/more/167699/jsjjgd/index.htm</x:v>
+      </x:c>
+      <x:c r="R28" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S28" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>历任讲师、副研究员、教授</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>上海交通大学微电子学院/微纳电子学系</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str"/>
+      <x:c r="G29" s="6" t="str"/>
+      <x:c r="H29" s="6" t="str"/>
+      <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str"/>
+      <x:c r="K29" s="6" t="str"/>
+      <x:c r="L29" s="6" t="str"/>
+      <x:c r="M29" s="7" t="str"/>
+      <x:c r="N29" s="6" t="str"/>
+      <x:c r="O29" s="6" t="str">
+        <x:v>来源仅称2006年底加入并先后任三职；未拆出各职称起止年份，现行组织以独立名录记录为准。</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="str"/>
+      <x:c r="Q29" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/heweifeng/zh_CN/more/167699/jsjjgd/index.htm</x:v>
+      </x:c>
+      <x:c r="R29" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S29" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>电子科技大学</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str"/>
+      <x:c r="F30" s="6" t="str"/>
+      <x:c r="G30" s="6" t="str">
+        <x:v>电子工程（electronic engineering，原文专业表述）</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I30" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J30" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L30" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M30" s="7" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="N30" s="6" t="str"/>
+      <x:c r="O30" s="6" t="str">
+        <x:v>作者简介明确received B.S. degree；不从授位年倒推入学或专业中文学科代码。</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q30" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="R30" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S30" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E31" s="6" t="str"/>
+      <x:c r="F31" s="6" t="str"/>
+      <x:c r="G31" s="6" t="str">
+        <x:v>电子工程（electronic engineering，原文专业表述）</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I31" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J31" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L31" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M31" s="7" t="str">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="N31" s="6" t="str"/>
+      <x:c r="O31" s="6" t="str">
+        <x:v>作者简介明确received Ph.D. degree；第三方旧转载称信息与通信工程，本包不据此覆盖第一方英文原词。</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q31" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="R31" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S31" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str"/>
+      <x:c r="F32" s="6" t="str"/>
+      <x:c r="G32" s="6" t="str"/>
+      <x:c r="H32" s="6" t="str"/>
+      <x:c r="I32" s="6" t="str"/>
+      <x:c r="J32" s="6" t="str"/>
+      <x:c r="K32" s="6" t="str"/>
+      <x:c r="L32" s="6" t="str"/>
+      <x:c r="M32" s="7" t="str"/>
+      <x:c r="N32" s="6" t="str"/>
+      <x:c r="O32" s="6" t="str">
+        <x:v>现行官方名录列示，不代表独立人事在岗核验；起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P32" s="6" t="str"/>
+      <x:c r="Q32" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="R32" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S32" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str"/>
+      <x:c r="F33" s="6" t="str"/>
+      <x:c r="G33" s="6" t="str">
+        <x:v>电气工程（electrical engineering，原文专业表述）</x:v>
+      </x:c>
+      <x:c r="H33" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I33" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J33" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K33" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L33" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M33" s="7" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="N33" s="6" t="str"/>
+      <x:c r="O33" s="6" t="str">
+        <x:v>论文作者简介明确received相应学位；学习起止与授位月未给，不由学位年份倒推。</x:v>
+      </x:c>
+      <x:c r="P33" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q33" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="R33" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S33" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>北京大学</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str"/>
+      <x:c r="F34" s="6" t="str"/>
+      <x:c r="G34" s="6" t="str">
+        <x:v>微电子学</x:v>
+      </x:c>
+      <x:c r="H34" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I34" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J34" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L34" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M34" s="7" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="N34" s="6" t="str"/>
+      <x:c r="O34" s="6" t="str">
+        <x:v>论文作者简介明确received相应学位；学习起止与授位月未给，不由学位年份倒推。</x:v>
+      </x:c>
+      <x:c r="P34" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q34" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="R34" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S34" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>利物浦约翰摩尔斯大学</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str"/>
+      <x:c r="F35" s="6" t="str"/>
+      <x:c r="G35" s="6" t="str">
+        <x:v>微电子学</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I35" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J35" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L35" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M35" s="7" t="str">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="N35" s="6" t="str"/>
+      <x:c r="O35" s="6" t="str">
+        <x:v>论文作者简介明确received相应学位；学习起止与授位月未给，不由学位年份倒推。 博士论文2010-06为提交封面日期，不等同授位月。</x:v>
+      </x:c>
+      <x:c r="P35" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q35" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="R35" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S35" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="str"/>
+      <x:c r="F36" s="6" t="str"/>
+      <x:c r="G36" s="6" t="str"/>
+      <x:c r="H36" s="6" t="str"/>
+      <x:c r="I36" s="6" t="str"/>
+      <x:c r="J36" s="6" t="str"/>
+      <x:c r="K36" s="6" t="str"/>
+      <x:c r="L36" s="6" t="str"/>
+      <x:c r="M36" s="7" t="str"/>
+      <x:c r="N36" s="6" t="str"/>
+      <x:c r="O36" s="6" t="str">
+        <x:v>现行官方名录列示，不代表独立人事在岗核验；起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P36" s="6" t="str"/>
+      <x:c r="Q36" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="R36" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S36" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>Reader</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>利物浦约翰摩尔斯大学</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="str"/>
+      <x:c r="F37" s="6" t="str"/>
+      <x:c r="G37" s="6" t="str"/>
+      <x:c r="H37" s="6" t="str"/>
+      <x:c r="I37" s="6" t="str"/>
+      <x:c r="J37" s="6" t="str"/>
+      <x:c r="K37" s="6" t="str"/>
+      <x:c r="L37" s="6" t="str"/>
+      <x:c r="M37" s="7" t="str"/>
+      <x:c r="N37" s="6" t="str"/>
+      <x:c r="O37" s="6" t="str">
+        <x:v>2020作者简介称加入上海交大之前任Reader；不使用旧论文现职作为当前状态，也不强行把Reader转换成中国职称。</x:v>
+      </x:c>
+      <x:c r="P37" s="6" t="str"/>
+      <x:c r="Q37" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="R37" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S37" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="str">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I38" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J38" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K38" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L38" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M38" s="7" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="N38" s="6" t="str"/>
+      <x:c r="O38" s="6" t="str">
+        <x:v>起止年由当前官网教育背景，学位实际取得与专业由第一方作者简介明确received支持；未给授位月份。</x:v>
+      </x:c>
+      <x:c r="P38" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q38" s="6" t="str">
+        <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
+      </x:c>
+      <x:c r="R38" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S38" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I39" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J39" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K39" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L39" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M39" s="7" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="N39" s="6" t="str"/>
+      <x:c r="O39" s="6" t="str">
+        <x:v>起止年由当前官网教育背景，学位实际取得与专业由第一方作者简介明确received支持；未给授位月份。</x:v>
+      </x:c>
+      <x:c r="P39" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q39" s="6" t="str">
+        <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
+      </x:c>
+      <x:c r="R39" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S39" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>加拿大阿尔伯塔大学（University of Alberta）</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>集成电路与系统</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="I40" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="J40" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L40" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M40" s="7" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="N40" s="6" t="str"/>
+      <x:c r="O40" s="6" t="str">
+        <x:v>起止年由当前官网教育背景，学位实际取得与专业由第一方作者简介明确received支持；未给授位月份。</x:v>
+      </x:c>
+      <x:c r="P40" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q40" s="6" t="str">
+        <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
+      </x:c>
+      <x:c r="R40" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S40" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>长聘教轨副教授</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str"/>
+      <x:c r="G41" s="6" t="str"/>
+      <x:c r="H41" s="6" t="str"/>
+      <x:c r="I41" s="6" t="str"/>
+      <x:c r="J41" s="6" t="str"/>
+      <x:c r="K41" s="6" t="str"/>
+      <x:c r="L41" s="6" t="str"/>
+      <x:c r="M41" s="7" t="str"/>
+      <x:c r="N41" s="6" t="str"/>
+      <x:c r="O41" s="6" t="str">
+        <x:v>官网工作经历明确2022年至今长聘教轨副教授；仅当前官方列示。</x:v>
+      </x:c>
+      <x:c r="P41" s="6" t="str"/>
+      <x:c r="Q41" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="R41" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S41" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>清华大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str"/>
+      <x:c r="H42" s="6" t="str"/>
+      <x:c r="I42" s="6" t="str"/>
+      <x:c r="J42" s="6" t="str"/>
+      <x:c r="K42" s="6" t="str"/>
+      <x:c r="L42" s="6" t="str"/>
+      <x:c r="M42" s="7" t="str"/>
+      <x:c r="N42" s="6" t="str"/>
+      <x:c r="O42" s="6" t="str">
+        <x:v>官网工作经历所列机构名称；非授位。论文写作当时称清华大学微电子所，不因名称演进拆成两段岗位。</x:v>
+      </x:c>
+      <x:c r="P42" s="6" t="str"/>
+      <x:c r="Q42" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="R42" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S42" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E43" s="6" t="str"/>
+      <x:c r="F43" s="6" t="str"/>
+      <x:c r="G43" s="6" t="str"/>
+      <x:c r="H43" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I43" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J43" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L43" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M43" s="7" t="str"/>
+      <x:c r="N43" s="6" t="str"/>
+      <x:c r="O43" s="6" t="str">
+        <x:v>官方教育段明确“获”对应工学学位，但未给任何学习或授位年份。</x:v>
+      </x:c>
+      <x:c r="P43" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q43" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R43" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S43" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E44" s="6" t="str"/>
+      <x:c r="F44" s="6" t="str"/>
+      <x:c r="G44" s="6" t="str">
+        <x:v>电路与系统</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I44" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J44" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L44" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M44" s="7" t="str"/>
+      <x:c r="N44" s="6" t="str"/>
+      <x:c r="O44" s="6" t="str">
+        <x:v>官方教育段明确“获”对应工学学位，但未给任何学习或授位年份。</x:v>
+      </x:c>
+      <x:c r="P44" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q44" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R44" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S44" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E45" s="6" t="str"/>
+      <x:c r="F45" s="6" t="str"/>
+      <x:c r="G45" s="6" t="str">
+        <x:v>电子科学与技术</x:v>
+      </x:c>
+      <x:c r="H45" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I45" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J45" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K45" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L45" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M45" s="7" t="str"/>
+      <x:c r="N45" s="6" t="str"/>
+      <x:c r="O45" s="6" t="str">
+        <x:v>官方教育段明确“获”对应工学学位，但未给任何学习或授位年份。</x:v>
+      </x:c>
+      <x:c r="P45" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问、博士后分开。</x:v>
+      </x:c>
+      <x:c r="Q45" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R45" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S45" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="str"/>
+      <x:c r="F46" s="6" t="str"/>
+      <x:c r="G46" s="6" t="str"/>
+      <x:c r="H46" s="6" t="str"/>
+      <x:c r="I46" s="6" t="str"/>
+      <x:c r="J46" s="6" t="str"/>
+      <x:c r="K46" s="6" t="str"/>
+      <x:c r="L46" s="6" t="str"/>
+      <x:c r="M46" s="7" t="str"/>
+      <x:c r="N46" s="6" t="str"/>
+      <x:c r="O46" s="6" t="str">
+        <x:v>现行官方名录列示，不代表独立人事在岗核验；起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P46" s="6" t="str"/>
+      <x:c r="Q46" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R46" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S46" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>美国北卡罗莱纳州立大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E47" s="6" t="str">
+        <x:v>2013-07</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str">
+        <x:v>2014-07</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str"/>
+      <x:c r="H47" s="6" t="str"/>
+      <x:c r="I47" s="6" t="str"/>
+      <x:c r="J47" s="6" t="str"/>
+      <x:c r="K47" s="6" t="str"/>
+      <x:c r="L47" s="6" t="str"/>
+      <x:c r="M47" s="7" t="str"/>
+      <x:c r="N47" s="6" t="str"/>
+      <x:c r="O47" s="6" t="str">
+        <x:v>非授位；导师/接待人未披露。</x:v>
+      </x:c>
+      <x:c r="P47" s="6" t="str"/>
+      <x:c r="Q47" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R47" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S47" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>比利时鲁汶大学及欧洲微电子中心（原文表述）</x:v>
+      </x:c>
+      <x:c r="E48" s="6" t="str">
+        <x:v>2016-10</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>2016-11</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str"/>
+      <x:c r="H48" s="6" t="str"/>
+      <x:c r="I48" s="6" t="str"/>
+      <x:c r="J48" s="6" t="str"/>
+      <x:c r="K48" s="6" t="str"/>
+      <x:c r="L48" s="6" t="str"/>
+      <x:c r="M48" s="7" t="str"/>
+      <x:c r="N48" s="6" t="str"/>
+      <x:c r="O48" s="6" t="str">
+        <x:v>原文将两机构合并在同一访问区间，未分配各自日期；不将访问当授位，不进一步猜校名法人消歧或导师。</x:v>
+      </x:c>
+      <x:c r="P48" s="6" t="str"/>
+      <x:c r="Q48" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="R48" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S48" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2466c93b234b54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b922592e56e4187"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1783,10 +3121,46 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>张建福</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>东南大学集成电路学院首席教授；曾任利物浦约翰摩尔斯大学微电子学教授，研究CMOS器件质量评估、老化与可靠性建模。</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>official_profile_indexed_current_role</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>东南大学现行官方主页检索内容列首席教授；会议主办方公开检索履历称2025年加入东南大学。后续独立HTTP下载403已停止，没有原始下载正文；不声称独立人事在岗核验，退休状态未知。</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str"/>
+      <x:c r="I3" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/1/518399.pdf</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>https://ic.seu.edu.cn/zjf/main.htm</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raccb790538b0494b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd212156ff7534b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2371,10 +3745,548 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>CCSA: A 394TOPS/W Mixed-signal GPS Accelerator with Charge-based Correlation Computing for Signal Acquisition</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str"/>
+      <x:c r="E17" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>A Metastability Risk Prediction and Mitigation Technique for Clock-Domain Crossing with Single-Stage Synchronizer in Near-Threshold-Voltage Multi-Voltage/Frequency Domain Network-on-Chip</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str"/>
+      <x:c r="E18" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>HyCTor: A Hybrid CNN-Transformer Network Accelerator with Flexible Weight/Output Stationary Dataflow and Multi-Core Extension</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>10.1109/TCAD.2024.3490173</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>journal_manuscript</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str">
+        <x:v>primary_full_text_read</x:v>
+      </x:c>
+      <x:c r="J19" s="6" t="str">
+        <x:v>已读2024作者接受稿，首页标明accepted for publication与DOI；2024指该稿版本，不据此断言最终卷期年份。</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>A 3.85 Gbps 8×8 Soft-Output MIMO Detector with Lattice-Reduction-Aided Channel Preprocessing</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Efficient and Robust RRAM-based Convolutional Weight Mapping with Shifted and Duplicated Kernel</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="I21" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>HyCTor: A Hybrid CNN-Transformer Network Accelerator with Flexible Weight/Output Stationary Dataflow and Multi-Core Extension</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>10.1109/TCAD.2024.3490173</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>journal_manuscript</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="I22" s="6" t="str">
+        <x:v>primary_full_text_read</x:v>
+      </x:c>
+      <x:c r="J22" s="6" t="str">
+        <x:v>2024作者接受稿，不是最终卷期核验。</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Characterization of negative bias temperature instability and lifetime prediction for pMOSFETs</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="I23" s="6" t="str">
+        <x:v>official_repository_record_and_thesis_read</x:v>
+      </x:c>
+      <x:c r="J23" s="6" t="str">
+        <x:v>正式校级机构库论文记录；论文PDF已读，授位信息另依作者简历。</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L23" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>An Assessment of the Statistical Distribution of Random Telegraph Noise Time Constants</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>10.1109/ACCESS.2020.3028747</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>primary_full_text_read</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>机构库论文首页与末页已读，附作者本人简历。</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>A Dual-Point technique for the entire ID-VG characterization into subthreshold region under Random Telegraph Noise condition</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Non-Volatile Approximate Arithmetic Circuits using Scalable Hybrid Spin-CMOS Majority Gates</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str"/>
+      <x:c r="E26" s="6" t="str">
+        <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str">
+        <x:v>official_list_and_author_manuscript_read</x:v>
+      </x:c>
+      <x:c r="J26" s="6" t="str">
+        <x:v>官网论文元数据与大学域名作者稿标题/作者一致；未独立核出版者全文。</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Beyond Uniform Approximation: Toward Efficient Computing in Logarithmic Number System for Large Language Models</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str"/>
+      <x:c r="E27" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="str">
+        <x:v>官网列2026；卷期、页码、DOI及最终出版状态未独立核验。</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>LUT-ALMs: Trading Off Accuracy and Power for Approximate Logarithmic Multipliers via LUT Optimization</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str"/>
+      <x:c r="E28" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="I28" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J28" s="6" t="str">
+        <x:v>官网列2026；卷期、页码、DOI及最终出版状态未独立核验。</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>DIONet3D: Dual-Input Dual-Output Deep Neural Network with 3D-Enhanced PDN Feature for IR Drop Prediction in 3D ICs</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>10.1109/TCAD.2026.3685522</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>https://ieeexplore.ieee.org/abstract/document/11488179</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="I29" s="6" t="str">
+        <x:v>publisher_metadata_indexed_body_unavailable</x:v>
+      </x:c>
+      <x:c r="J29" s="6" t="str">
+        <x:v>本人官网书目确认身份；DOI与Early Access元数据来自出版者检索记录。出版者正文418后停止，不能声称全文已读。</x:v>
+      </x:c>
+      <x:c r="K29" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L29" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>A 51.19 mm², 4 TB/s bandwidth 3D Logic-on-SRAM Stacking CGRA Chip</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str"/>
+      <x:c r="E30" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="I30" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J30" s="6" t="str">
+        <x:v>仅官网精选书目；单篇出版者链接未核。</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L30" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>An Energy Efficient CPU-FPGA Heterogeneous Acceleration System for Third-Generation Genomic Sequencing Based on Minimap2</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str"/>
+      <x:c r="E31" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="I31" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J31" s="6" t="str">
+        <x:v>仅官网精选书目；单篇出版者链接未核。</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b3306c74d7a43e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701587f6528641f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2762,16 +4674,16 @@
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
-        <x:v>陈海宝</x:v>
+        <x:v>何卫锋</x:v>
       </x:c>
       <x:c r="B17" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>heweifeng-source-1</x:v>
       </x:c>
       <x:c r="C17" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_previously_read</x:v>
       </x:c>
       <x:c r="E17" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -2785,16 +4697,16 @@
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
-        <x:v>郭衍束</x:v>
+        <x:v>何卫锋</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>heweifeng-source-2</x:v>
       </x:c>
       <x:c r="C18" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_public_body_read</x:v>
       </x:c>
       <x:c r="E18" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -2803,13 +4715,611 @@
         <x:v>sjtu</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>heweifeng-source-3</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/heweifeng/zh_CN/more/167699/jsjjgd/index.htm</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>heweifeng-source-4</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>official_hosted_author_manuscript_read</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>heguanghui-source-1</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>official_roster_previously_read</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>heguanghui-source-2</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>heguanghui-source-3</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>official_hosted_author_manuscript_read</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>jizhigang-source-1</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>official_roster_previously_read</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>jizhigang-source-2</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>jizhigang-source-3</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>institutional_repository_paper_read</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>jizhigang-source-4</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/1/518399.pdf</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>official_repository_thesis_read</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>jizhigang-source-5</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>official_repository_metadata_read</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>jizhigang-source-6</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>https://ic.seu.edu.cn/zjf/main.htm</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>official_indexed_profile_read_before_direct_http403</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>jizhigang-source-7</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>https://www.semiconchina.org/zh/2327</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>official_indexed_profile_read_before_direct_http403</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>jianghonglan-source-1</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>official_roster_previously_read</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>jianghonglan-source-2</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>jianghonglan-source-3</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>official_hosted_author_manuscript_read</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>jiangjianfei-source-1</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>official_roster_previously_read</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>jiangjianfei-source-2</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>jiangjianfei-source-3</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str">
+        <x:v>https://ieeexplore.ieee.org/abstract/document/11488179</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>indexed_primary_metadata_body_unavailable</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>陈海宝</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>郭衍束</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>蒋剑飞</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bbdf650b2494ec7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b7092afe4634f12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd2177746abfe4a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rc0f9b47166774fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ree80284d7f634f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R9c9682b0531f461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rb5417d9c192f465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R790ef1d19bd649eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R498a7d4502784c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R13d33f438ee744e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R0bd985b136ce4b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rd4742dbe411b4139"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T8_0" displayName="T8_0" ref="A1:K11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T8_0" displayName="T8_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T8_1" displayName="T8_1" ref="A1:S48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T8_1" displayName="T8_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T8_3" displayName="T8_3" ref="A1:L31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T8_3" displayName="T8_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T8_4" displayName="T8_4" ref="A1:G44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T8_4" displayName="T8_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -812,10 +812,307 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>当前学院研究员与研究生院个人页教授两标签不一致，保留来源差异，不猜晋升月份。；学历起始年份、硕士经历及导师未核；共同作者周健军不自动当博士导师。</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>景乃锋</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jingnaifeng.html</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>本科硕士学校/年月、导师未独立直接核。；候选教师平台地址404不继续猜URL；现行研究员与2021副教授分时记录。</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>基金会2013使用will be advisor，为当时计划，不能单独升级已完成博士导师；IMS2018明确Advisor只按论文竞赛指导建边，不冒称博士学位指导。；学位具体专业、学位导师、公司详细任职仍待核。</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liyongfu.html</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>学位年月/导师、加入上交年份未披露；不得按2013研究工程师起点猜博士毕业年。；新学院长聘副教授与旧实验室长聘教轨副教授为来源版本差异，不推晋升年月。；未取得逐篇论文，本轮保留空精选目录。</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>未取得明确导师原文；不由合著或学生栏目推师承，论文仅官网精选。</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/maozhigang.html</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>当前学院页身份研究方向直接核；详细教育/历史任职仅校方检索索引，直接主页超时，不宣称正文验证。；硕士院校仅中文高等电气学校，不由第三方转载强定地理；导师和独立成果链接未核。</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>博士导师仅官方索引候选，访问交流导师未明确，不用共同作者推断。；澳门作者PDF503、2025会议册502未直接读取；学位取得可后续独立补证，保留学习期间。</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>未取得明确导师原文；不由合著或学生栏目推师承，论文仅官网精选。；本科学士与博士仅学习经历学位标签，明确授位状态待补证；不能将学习结束月当授位月。</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>集成电路学院（信息与电子工程学院）·芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>学历经历已核但授位状态仍保守；与毛志刚/肖立伊合著不等于导师。；旧主页Research Assistant Professor与当前副研究员分时保留，晋升时间未知。</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93a5ee5e9404537"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4dcd7d1bfac4c1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3019,10 +3316,2476 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>南京理工大学</x:v>
+      </x:c>
+      <x:c r="E49" s="6" t="str"/>
+      <x:c r="F49" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>电子信息工程</x:v>
+      </x:c>
+      <x:c r="H49" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I49" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J49" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K49" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L49" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M49" s="7" t="str"/>
+      <x:c r="N49" s="6" t="str"/>
+      <x:c r="O49" s="6" t="str">
+        <x:v>出版者作者简介明确received；同名同上交微电子/CARFIC射频专业身份，不合并外国语学院金晶或华东理工脑机接口金晶。</x:v>
+      </x:c>
+      <x:c r="P49" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q49" s="6" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
+      </x:c>
+      <x:c r="R49" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S49" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E50" s="6" t="str"/>
+      <x:c r="F50" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>电子科学与技术</x:v>
+      </x:c>
+      <x:c r="H50" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I50" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J50" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K50" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L50" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M50" s="7" t="str"/>
+      <x:c r="N50" s="6" t="str"/>
+      <x:c r="O50" s="6" t="str"/>
+      <x:c r="P50" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q50" s="6" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
+      </x:c>
+      <x:c r="R50" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S50" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E51" s="6" t="str"/>
+      <x:c r="F51" s="6" t="str"/>
+      <x:c r="G51" s="6" t="str"/>
+      <x:c r="H51" s="6" t="str"/>
+      <x:c r="I51" s="6" t="str"/>
+      <x:c r="J51" s="6" t="str"/>
+      <x:c r="K51" s="6" t="str"/>
+      <x:c r="L51" s="6" t="str"/>
+      <x:c r="M51" s="7" t="str"/>
+      <x:c r="N51" s="6" t="str"/>
+      <x:c r="O51" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P51" s="6" t="str"/>
+      <x:c r="Q51" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
+      </x:c>
+      <x:c r="R51" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S51" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>所长</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>上海交通大学芯片设计与EDA研究所</x:v>
+      </x:c>
+      <x:c r="E52" s="6" t="str"/>
+      <x:c r="F52" s="6" t="str"/>
+      <x:c r="G52" s="6" t="str"/>
+      <x:c r="H52" s="6" t="str"/>
+      <x:c r="I52" s="6" t="str"/>
+      <x:c r="J52" s="6" t="str"/>
+      <x:c r="K52" s="6" t="str"/>
+      <x:c r="L52" s="6" t="str"/>
+      <x:c r="M52" s="7" t="str"/>
+      <x:c r="N52" s="6" t="str"/>
+      <x:c r="O52" s="6" t="str"/>
+      <x:c r="P52" s="6" t="str"/>
+      <x:c r="Q52" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
+      </x:c>
+      <x:c r="R52" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S52" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>教授（研究生院本人页列示）</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E53" s="6" t="str"/>
+      <x:c r="F53" s="6" t="str"/>
+      <x:c r="G53" s="6" t="str"/>
+      <x:c r="H53" s="6" t="str"/>
+      <x:c r="I53" s="6" t="str"/>
+      <x:c r="J53" s="6" t="str"/>
+      <x:c r="K53" s="6" t="str"/>
+      <x:c r="L53" s="6" t="str"/>
+      <x:c r="M53" s="7" t="str"/>
+      <x:c r="N53" s="6" t="str"/>
+      <x:c r="O53" s="6" t="str">
+        <x:v>当前学院页研究员、研究生院本人页教授，不选一消除，职称差异待核。</x:v>
+      </x:c>
+      <x:c r="P53" s="6" t="str"/>
+      <x:c r="Q53" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/jinjing1/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R53" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S53" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>景乃锋</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E54" s="6" t="str"/>
+      <x:c r="F54" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str"/>
+      <x:c r="H54" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I54" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J54" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K54" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L54" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M54" s="7" t="str"/>
+      <x:c r="N54" s="6" t="str"/>
+      <x:c r="O54" s="6" t="str">
+        <x:v>2021作者简介明确received；本科硕士年份未取得直接原始证据，不从第三方简介补入。</x:v>
+      </x:c>
+      <x:c r="P54" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q54" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
+      </x:c>
+      <x:c r="R54" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S54" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>景乃锋</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E55" s="6" t="str"/>
+      <x:c r="F55" s="6" t="str"/>
+      <x:c r="G55" s="6" t="str"/>
+      <x:c r="H55" s="6" t="str"/>
+      <x:c r="I55" s="6" t="str"/>
+      <x:c r="J55" s="6" t="str"/>
+      <x:c r="K55" s="6" t="str"/>
+      <x:c r="L55" s="6" t="str"/>
+      <x:c r="M55" s="7" t="str"/>
+      <x:c r="N55" s="6" t="str"/>
+      <x:c r="O55" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P55" s="6" t="str"/>
+      <x:c r="Q55" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jingnaifeng.html</x:v>
+      </x:c>
+      <x:c r="R55" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S55" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>景乃锋</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>副教授（2021论文时点）</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>上海交通大学微纳电子学系</x:v>
+      </x:c>
+      <x:c r="E56" s="6" t="str"/>
+      <x:c r="F56" s="6" t="str"/>
+      <x:c r="G56" s="6" t="str"/>
+      <x:c r="H56" s="6" t="str"/>
+      <x:c r="I56" s="6" t="str"/>
+      <x:c r="J56" s="6" t="str"/>
+      <x:c r="K56" s="6" t="str"/>
+      <x:c r="L56" s="6" t="str"/>
+      <x:c r="M56" s="7" t="str"/>
+      <x:c r="N56" s="6" t="str"/>
+      <x:c r="O56" s="6" t="str"/>
+      <x:c r="P56" s="6" t="str"/>
+      <x:c r="Q56" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
+      </x:c>
+      <x:c r="R56" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S56" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E57" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>微电子学院（院系）</x:v>
+      </x:c>
+      <x:c r="H57" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I57" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J57" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K57" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L57" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M57" s="7" t="str"/>
+      <x:c r="N57" s="6" t="str"/>
+      <x:c r="O57" s="6" t="str">
+        <x:v>奖学金机构本人简历明确received；入学年另由当前学院页教育区间支持。</x:v>
+      </x:c>
+      <x:c r="P57" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q57" s="6" t="str">
+        <x:v>https://irvingthofoundation.github.io/fellow-biographies-sobi2Task=sobi2Details&amp;sobi2Id=55.htm</x:v>
+      </x:c>
+      <x:c r="R57" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S57" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E58" s="6" t="str">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str">
+        <x:v>微电子学院（院系）</x:v>
+      </x:c>
+      <x:c r="H58" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I58" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J58" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K58" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L58" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M58" s="7" t="str"/>
+      <x:c r="N58" s="6" t="str"/>
+      <x:c r="O58" s="6" t="str"/>
+      <x:c r="P58" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q58" s="6" t="str">
+        <x:v>https://irvingthofoundation.github.io/fellow-biographies-sobi2Task=sobi2Details&amp;sobi2Id=55.htm</x:v>
+      </x:c>
+      <x:c r="R58" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S58" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>加州大学戴维斯分校</x:v>
+      </x:c>
+      <x:c r="E59" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str"/>
+      <x:c r="H59" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I59" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J59" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K59" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L59" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M59" s="7" t="str"/>
+      <x:c r="N59" s="6" t="str"/>
+      <x:c r="O59" s="6" t="str">
+        <x:v>当前学院明言2019获得博士；基金会明确2013入学，与姓名/上交2010/2013学历序列匹配。</x:v>
+      </x:c>
+      <x:c r="P59" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q59" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="R59" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S59" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>长聘教轨副教授</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E60" s="6" t="str"/>
+      <x:c r="F60" s="6" t="str"/>
+      <x:c r="G60" s="6" t="str"/>
+      <x:c r="H60" s="6" t="str"/>
+      <x:c r="I60" s="6" t="str"/>
+      <x:c r="J60" s="6" t="str"/>
+      <x:c r="K60" s="6" t="str"/>
+      <x:c r="L60" s="6" t="str"/>
+      <x:c r="M60" s="7" t="str"/>
+      <x:c r="N60" s="6" t="str"/>
+      <x:c r="O60" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P60" s="6" t="str"/>
+      <x:c r="Q60" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="R60" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S60" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="str">
+        <x:v>无线通信射频、模拟和混合信号芯片研发</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
+        <x:v>美国硅谷科技公司（未逐家披露）</x:v>
+      </x:c>
+      <x:c r="E61" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str"/>
+      <x:c r="H61" s="6" t="str"/>
+      <x:c r="I61" s="6" t="str"/>
+      <x:c r="J61" s="6" t="str"/>
+      <x:c r="K61" s="6" t="str"/>
+      <x:c r="L61" s="6" t="str"/>
+      <x:c r="M61" s="7" t="str"/>
+      <x:c r="N61" s="6" t="str"/>
+      <x:c r="O61" s="6" t="str">
+        <x:v>官方叙述博士后在公司研发、2025加入上交；不是博士后研究员，具体公司及离职月未知。</x:v>
+      </x:c>
+      <x:c r="P61" s="6" t="str"/>
+      <x:c r="Q61" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="R61" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S61" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>长聘教轨副教授、博士生导师</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E62" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F62" s="6" t="str"/>
+      <x:c r="G62" s="6" t="str"/>
+      <x:c r="H62" s="6" t="str"/>
+      <x:c r="I62" s="6" t="str"/>
+      <x:c r="J62" s="6" t="str"/>
+      <x:c r="K62" s="6" t="str"/>
+      <x:c r="L62" s="6" t="str"/>
+      <x:c r="M62" s="7" t="str"/>
+      <x:c r="N62" s="6" t="str"/>
+      <x:c r="O62" s="6" t="str"/>
+      <x:c r="P62" s="6" t="str"/>
+      <x:c r="Q62" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="R62" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S62" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>project_guidance</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>项目指导（非学位师承）</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str"/>
+      <x:c r="E63" s="6" t="str"/>
+      <x:c r="F63" s="6" t="str"/>
+      <x:c r="G63" s="6" t="str"/>
+      <x:c r="H63" s="6" t="str"/>
+      <x:c r="I63" s="6" t="str"/>
+      <x:c r="J63" s="6" t="str"/>
+      <x:c r="K63" s="6" t="str"/>
+      <x:c r="L63" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="7" t="str"/>
+      <x:c r="N63" s="6" t="str"/>
+      <x:c r="O63" s="6" t="str">
+        <x:v>Qun Jane Gu；竞赛项目指导（非学位师承）；博士学习期间学生论文竞赛指导（非已核学位导师）；IMS2018 student paper competition Advisor; not asserted dissertation supervisor；加州大学戴维斯分校电气与计算机工程教授、HSICS实验室负责人。；UC Davis官方页列2020起Professor，访问可读。；IMS2018竞赛研究项目指导，不是确证博士学位指导；不进学位师承主图。；独立项目指导事实，不进入学位师承主图或导师计数。；非学位师承，不计入导师统计或师承关系图；https://www.ece.ucdavis.edu/hsics/jane-gu/</x:v>
+      </x:c>
+      <x:c r="P63" s="6" t="str"/>
+      <x:c r="Q63" s="6" t="str">
+        <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
+      </x:c>
+      <x:c r="R63" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S63" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E64" s="6" t="str"/>
+      <x:c r="F64" s="6" t="str"/>
+      <x:c r="G64" s="6" t="str">
+        <x:v>电气与计算工程系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H64" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I64" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J64" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K64" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L64" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M64" s="7" t="str"/>
+      <x:c r="N64" s="6" t="str"/>
+      <x:c r="O64" s="6" t="str">
+        <x:v>大学官方实验室直接链接本人站，Biography明确received B.Eng. and Ph.D.，年月未列。</x:v>
+      </x:c>
+      <x:c r="P64" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q64" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R64" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S64" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C65" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E65" s="6" t="str"/>
+      <x:c r="F65" s="6" t="str"/>
+      <x:c r="G65" s="6" t="str">
+        <x:v>电气与计算工程系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H65" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I65" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J65" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K65" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L65" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M65" s="7" t="str"/>
+      <x:c r="N65" s="6" t="str"/>
+      <x:c r="O65" s="6" t="str">
+        <x:v>大学官方实验室直接链接本人站，Biography明确received B.Eng. and Ph.D.，年月未列。</x:v>
+      </x:c>
+      <x:c r="P65" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q65" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R65" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S65" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>长聘副教授</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E66" s="6" t="str"/>
+      <x:c r="F66" s="6" t="str"/>
+      <x:c r="G66" s="6" t="str"/>
+      <x:c r="H66" s="6" t="str"/>
+      <x:c r="I66" s="6" t="str"/>
+      <x:c r="J66" s="6" t="str"/>
+      <x:c r="K66" s="6" t="str"/>
+      <x:c r="L66" s="6" t="str"/>
+      <x:c r="M66" s="7" t="str"/>
+      <x:c r="N66" s="6" t="str"/>
+      <x:c r="O66" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P66" s="6" t="str"/>
+      <x:c r="Q66" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liyongfu.html</x:v>
+      </x:c>
+      <x:c r="R66" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S66" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>Research Engineer</x:v>
+      </x:c>
+      <x:c r="D67" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E67" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="F67" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="G67" s="6" t="str"/>
+      <x:c r="H67" s="6" t="str"/>
+      <x:c r="I67" s="6" t="str"/>
+      <x:c r="J67" s="6" t="str"/>
+      <x:c r="K67" s="6" t="str"/>
+      <x:c r="L67" s="6" t="str"/>
+      <x:c r="M67" s="7" t="str"/>
+      <x:c r="N67" s="6" t="str"/>
+      <x:c r="O67" s="6" t="str"/>
+      <x:c r="P67" s="6" t="str"/>
+      <x:c r="Q67" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R67" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S67" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str">
+        <x:v>Senior Engineer</x:v>
+      </x:c>
+      <x:c r="D68" s="6" t="str">
+        <x:v>GLOBALFOUNDRIES</x:v>
+      </x:c>
+      <x:c r="E68" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str"/>
+      <x:c r="H68" s="6" t="str"/>
+      <x:c r="I68" s="6" t="str"/>
+      <x:c r="J68" s="6" t="str"/>
+      <x:c r="K68" s="6" t="str"/>
+      <x:c r="L68" s="6" t="str"/>
+      <x:c r="M68" s="7" t="str"/>
+      <x:c r="N68" s="6" t="str"/>
+      <x:c r="O68" s="6" t="str"/>
+      <x:c r="P68" s="6" t="str"/>
+      <x:c r="Q68" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R68" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S68" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C69" s="6" t="str">
+        <x:v>Principal Engineer</x:v>
+      </x:c>
+      <x:c r="D69" s="6" t="str">
+        <x:v>GLOBALFOUNDRIES</x:v>
+      </x:c>
+      <x:c r="E69" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="F69" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G69" s="6" t="str"/>
+      <x:c r="H69" s="6" t="str"/>
+      <x:c r="I69" s="6" t="str"/>
+      <x:c r="J69" s="6" t="str"/>
+      <x:c r="K69" s="6" t="str"/>
+      <x:c r="L69" s="6" t="str"/>
+      <x:c r="M69" s="7" t="str"/>
+      <x:c r="N69" s="6" t="str"/>
+      <x:c r="O69" s="6" t="str"/>
+      <x:c r="P69" s="6" t="str"/>
+      <x:c r="Q69" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R69" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S69" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C70" s="6" t="str">
+        <x:v>Member of Technical Staff</x:v>
+      </x:c>
+      <x:c r="D70" s="6" t="str">
+        <x:v>GLOBALFOUNDRIES</x:v>
+      </x:c>
+      <x:c r="E70" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F70" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="str"/>
+      <x:c r="H70" s="6" t="str"/>
+      <x:c r="I70" s="6" t="str"/>
+      <x:c r="J70" s="6" t="str"/>
+      <x:c r="K70" s="6" t="str"/>
+      <x:c r="L70" s="6" t="str"/>
+      <x:c r="M70" s="7" t="str"/>
+      <x:c r="N70" s="6" t="str"/>
+      <x:c r="O70" s="6" t="str"/>
+      <x:c r="P70" s="6" t="str"/>
+      <x:c r="Q70" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="R70" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S70" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C71" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D71" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E71" s="6" t="str"/>
+      <x:c r="F71" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="str"/>
+      <x:c r="H71" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I71" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J71" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K71" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L71" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M71" s="7" t="str"/>
+      <x:c r="N71" s="6" t="str"/>
+      <x:c r="O71" s="6" t="str"/>
+      <x:c r="P71" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q71" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R71" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S71" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="64" customHeight="1">
+      <x:c r="A72" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B72" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C72" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D72" s="6" t="str">
+        <x:v>帝国理工学院</x:v>
+      </x:c>
+      <x:c r="E72" s="6" t="str"/>
+      <x:c r="F72" s="6" t="str">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="G72" s="6" t="str">
+        <x:v>Electrical and Electronic Engineering</x:v>
+      </x:c>
+      <x:c r="H72" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I72" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J72" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K72" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L72" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M72" s="7" t="str"/>
+      <x:c r="N72" s="6" t="str"/>
+      <x:c r="O72" s="6" t="str"/>
+      <x:c r="P72" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q72" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R72" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S72" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
+      <x:c r="A73" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B73" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C73" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D73" s="6" t="str">
+        <x:v>帝国理工学院</x:v>
+      </x:c>
+      <x:c r="E73" s="6" t="str">
+        <x:v>2008-01-14</x:v>
+      </x:c>
+      <x:c r="F73" s="6" t="str">
+        <x:v>2012-03-01</x:v>
+      </x:c>
+      <x:c r="G73" s="6" t="str">
+        <x:v>Electrical and Electronic Engineering</x:v>
+      </x:c>
+      <x:c r="H73" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I73" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J73" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K73" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L73" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M73" s="7" t="str"/>
+      <x:c r="N73" s="6" t="str"/>
+      <x:c r="O73" s="6" t="str">
+        <x:v>日期为官方DEGREES区间，非独立学位授予日。</x:v>
+      </x:c>
+      <x:c r="P73" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q73" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R73" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S73" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
+      <x:c r="A74" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B74" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C74" s="6" t="str"/>
+      <x:c r="D74" s="6" t="str">
+        <x:v>帝国理工学院</x:v>
+      </x:c>
+      <x:c r="E74" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="F74" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G74" s="6" t="str"/>
+      <x:c r="H74" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I74" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J74" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K74" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L74" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M74" s="7" t="str"/>
+      <x:c r="N74" s="6" t="str"/>
+      <x:c r="O74" s="6" t="str">
+        <x:v>简介描述postdoc期间Research Associate/Research Fellow，两职级起讫未分。</x:v>
+      </x:c>
+      <x:c r="P74" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q74" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R74" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S74" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
+      <x:c r="A75" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B75" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D75" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E75" s="6" t="str"/>
+      <x:c r="F75" s="6" t="str"/>
+      <x:c r="G75" s="6" t="str"/>
+      <x:c r="H75" s="6" t="str"/>
+      <x:c r="I75" s="6" t="str"/>
+      <x:c r="J75" s="6" t="str"/>
+      <x:c r="K75" s="6" t="str"/>
+      <x:c r="L75" s="6" t="str"/>
+      <x:c r="M75" s="7" t="str"/>
+      <x:c r="N75" s="6" t="str"/>
+      <x:c r="O75" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P75" s="6" t="str"/>
+      <x:c r="Q75" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="R75" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S75" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
+      <x:c r="A76" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B76" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C76" s="6" t="str">
+        <x:v>Research Associate / Research Fellow</x:v>
+      </x:c>
+      <x:c r="D76" s="6" t="str">
+        <x:v>帝国理工学院NGNI Lab</x:v>
+      </x:c>
+      <x:c r="E76" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="F76" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G76" s="6" t="str"/>
+      <x:c r="H76" s="6" t="str"/>
+      <x:c r="I76" s="6" t="str"/>
+      <x:c r="J76" s="6" t="str"/>
+      <x:c r="K76" s="6" t="str"/>
+      <x:c r="L76" s="6" t="str"/>
+      <x:c r="M76" s="7" t="str"/>
+      <x:c r="N76" s="6" t="str"/>
+      <x:c r="O76" s="6" t="str"/>
+      <x:c r="P76" s="6" t="str"/>
+      <x:c r="Q76" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R76" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S76" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
+      <x:c r="A77" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B77" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C77" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D77" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E77" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="F77" s="6" t="str"/>
+      <x:c r="G77" s="6" t="str"/>
+      <x:c r="H77" s="6" t="str"/>
+      <x:c r="I77" s="6" t="str"/>
+      <x:c r="J77" s="6" t="str"/>
+      <x:c r="K77" s="6" t="str"/>
+      <x:c r="L77" s="6" t="str"/>
+      <x:c r="M77" s="7" t="str"/>
+      <x:c r="N77" s="6" t="str"/>
+      <x:c r="O77" s="6" t="str"/>
+      <x:c r="P77" s="6" t="str"/>
+      <x:c r="Q77" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R77" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S77" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
+      <x:c r="A78" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B78" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C78" s="6" t="str">
+        <x:v>Honorary Senior Lecturer / Visiting Academic</x:v>
+      </x:c>
+      <x:c r="D78" s="6" t="str">
+        <x:v>帝国理工学院</x:v>
+      </x:c>
+      <x:c r="E78" s="6" t="str"/>
+      <x:c r="F78" s="6" t="str"/>
+      <x:c r="G78" s="6" t="str"/>
+      <x:c r="H78" s="6" t="str"/>
+      <x:c r="I78" s="6" t="str"/>
+      <x:c r="J78" s="6" t="str"/>
+      <x:c r="K78" s="6" t="str"/>
+      <x:c r="L78" s="6" t="str"/>
+      <x:c r="M78" s="7" t="str"/>
+      <x:c r="N78" s="6" t="str"/>
+      <x:c r="O78" s="6" t="str">
+        <x:v>名誉及访问身份，不推定全职双聘。</x:v>
+      </x:c>
+      <x:c r="P78" s="6" t="str"/>
+      <x:c r="Q78" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="R78" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S78" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="64" customHeight="1">
+      <x:c r="A79" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B79" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C79" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D79" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E79" s="6" t="str">
+        <x:v>1981-09</x:v>
+      </x:c>
+      <x:c r="F79" s="6" t="str">
+        <x:v>1986-07</x:v>
+      </x:c>
+      <x:c r="G79" s="6" t="str">
+        <x:v>微电子学与固体电子学</x:v>
+      </x:c>
+      <x:c r="H79" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I79" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J79" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K79" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L79" s="6" t="str"/>
+      <x:c r="M79" s="7" t="str"/>
+      <x:c r="N79" s="6" t="str"/>
+      <x:c r="O79" s="6" t="str">
+        <x:v>校方主页搜索索引明确学位名称和毕业，直接页面超时未读，本批保守待授位核；高等电气学校原名不擅自归一。</x:v>
+      </x:c>
+      <x:c r="P79" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q79" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="R79" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S79" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64" customHeight="1">
+      <x:c r="A80" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B80" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C80" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D80" s="6" t="str">
+        <x:v>高等电气学校</x:v>
+      </x:c>
+      <x:c r="E80" s="6" t="str">
+        <x:v>1987-09</x:v>
+      </x:c>
+      <x:c r="F80" s="6" t="str">
+        <x:v>1988-07</x:v>
+      </x:c>
+      <x:c r="G80" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H80" s="6" t="str"/>
+      <x:c r="I80" s="6" t="str"/>
+      <x:c r="J80" s="6" t="str"/>
+      <x:c r="K80" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L80" s="6" t="str"/>
+      <x:c r="M80" s="7" t="str"/>
+      <x:c r="N80" s="6" t="str"/>
+      <x:c r="O80" s="6" t="str">
+        <x:v>校方主页搜索索引明确学位名称和毕业，直接页面超时未读，本批保守待授位核；高等电气学校原名不擅自归一。</x:v>
+      </x:c>
+      <x:c r="P80" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q80" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="R80" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S80" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="64" customHeight="1">
+      <x:c r="A81" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B81" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C81" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D81" s="6" t="str">
+        <x:v>University of Rennes</x:v>
+      </x:c>
+      <x:c r="E81" s="6" t="str">
+        <x:v>1988-09</x:v>
+      </x:c>
+      <x:c r="F81" s="6" t="str">
+        <x:v>1992-01</x:v>
+      </x:c>
+      <x:c r="G81" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H81" s="6" t="str">
+        <x:v>法国</x:v>
+      </x:c>
+      <x:c r="I81" s="6" t="str">
+        <x:v>法国</x:v>
+      </x:c>
+      <x:c r="J81" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K81" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L81" s="6" t="str"/>
+      <x:c r="M81" s="7" t="str"/>
+      <x:c r="N81" s="6" t="str"/>
+      <x:c r="O81" s="6" t="str">
+        <x:v>校方主页搜索索引明确学位名称和毕业，直接页面超时未读，本批保守待授位核；高等电气学校原名不擅自归一。</x:v>
+      </x:c>
+      <x:c r="P81" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q81" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="R81" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S81" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="64" customHeight="1">
+      <x:c r="A82" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B82" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C82" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D82" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E82" s="6" t="str"/>
+      <x:c r="F82" s="6" t="str"/>
+      <x:c r="G82" s="6" t="str"/>
+      <x:c r="H82" s="6" t="str"/>
+      <x:c r="I82" s="6" t="str"/>
+      <x:c r="J82" s="6" t="str"/>
+      <x:c r="K82" s="6" t="str"/>
+      <x:c r="L82" s="6" t="str"/>
+      <x:c r="M82" s="7" t="str"/>
+      <x:c r="N82" s="6" t="str"/>
+      <x:c r="O82" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P82" s="6" t="str"/>
+      <x:c r="Q82" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/maozhigang.html</x:v>
+      </x:c>
+      <x:c r="R82" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S82" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
+      <x:c r="A83" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B83" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C83" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D83" s="6" t="str">
+        <x:v>哈尔滨工业大学航天学院</x:v>
+      </x:c>
+      <x:c r="E83" s="6" t="str">
+        <x:v>1992-03</x:v>
+      </x:c>
+      <x:c r="F83" s="6" t="str">
+        <x:v>2009-08</x:v>
+      </x:c>
+      <x:c r="G83" s="6" t="str"/>
+      <x:c r="H83" s="6" t="str"/>
+      <x:c r="I83" s="6" t="str"/>
+      <x:c r="J83" s="6" t="str"/>
+      <x:c r="K83" s="6" t="str"/>
+      <x:c r="L83" s="6" t="str"/>
+      <x:c r="M83" s="7" t="str"/>
+      <x:c r="N83" s="6" t="str"/>
+      <x:c r="O83" s="6" t="str">
+        <x:v>校方搜索索引；两校2009夏重叠保留，不自行改月份。</x:v>
+      </x:c>
+      <x:c r="P83" s="6" t="str"/>
+      <x:c r="Q83" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="R83" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S83" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
+      <x:c r="A84" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B84" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C84" s="6" t="str">
+        <x:v>教学科研</x:v>
+      </x:c>
+      <x:c r="D84" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E84" s="6" t="str">
+        <x:v>2009-07</x:v>
+      </x:c>
+      <x:c r="F84" s="6" t="str"/>
+      <x:c r="G84" s="6" t="str"/>
+      <x:c r="H84" s="6" t="str"/>
+      <x:c r="I84" s="6" t="str"/>
+      <x:c r="J84" s="6" t="str"/>
+      <x:c r="K84" s="6" t="str"/>
+      <x:c r="L84" s="6" t="str"/>
+      <x:c r="M84" s="7" t="str"/>
+      <x:c r="N84" s="6" t="str"/>
+      <x:c r="O84" s="6" t="str">
+        <x:v>校方搜索索引；两校2009夏重叠保留，不自行改月份。</x:v>
+      </x:c>
+      <x:c r="P84" s="6" t="str"/>
+      <x:c r="Q84" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="R84" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S84" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="64" customHeight="1">
+      <x:c r="A85" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B85" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C85" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D85" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E85" s="6" t="str">
+        <x:v>2008-08</x:v>
+      </x:c>
+      <x:c r="F85" s="6" t="str">
+        <x:v>2012-07</x:v>
+      </x:c>
+      <x:c r="G85" s="6" t="str"/>
+      <x:c r="H85" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I85" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J85" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K85" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L85" s="6" t="str"/>
+      <x:c r="M85" s="7" t="str"/>
+      <x:c r="N85" s="6" t="str"/>
+      <x:c r="O85" s="6" t="str">
+        <x:v>官网教育区间仅学士标签，补证会议简介为索引，暂null。</x:v>
+      </x:c>
+      <x:c r="P85" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q85" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R85" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S85" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64" customHeight="1">
+      <x:c r="A86" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B86" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C86" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D86" s="6" t="str">
+        <x:v>澳门大学</x:v>
+      </x:c>
+      <x:c r="E86" s="6" t="str">
+        <x:v>2012-08</x:v>
+      </x:c>
+      <x:c r="F86" s="6" t="str">
+        <x:v>2019-10</x:v>
+      </x:c>
+      <x:c r="G86" s="6" t="str"/>
+      <x:c r="H86" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I86" s="6" t="str">
+        <x:v>中国澳门</x:v>
+      </x:c>
+      <x:c r="J86" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K86" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L86" s="6" t="str"/>
+      <x:c r="M86" s="7" t="str"/>
+      <x:c r="N86" s="6" t="str"/>
+      <x:c r="O86" s="6" t="str">
+        <x:v>官网明确博士毕业，但本次未直接读取独立received学位证据，保留博士学习；不把交流德国归为博士授位地。</x:v>
+      </x:c>
+      <x:c r="P86" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q86" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R86" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S86" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64" customHeight="1">
+      <x:c r="A87" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B87" s="6" t="str">
+        <x:v>visiting_research</x:v>
+      </x:c>
+      <x:c r="C87" s="6" t="str"/>
+      <x:c r="D87" s="6" t="str">
+        <x:v>乌尔姆大学</x:v>
+      </x:c>
+      <x:c r="E87" s="6" t="str">
+        <x:v>2016-08</x:v>
+      </x:c>
+      <x:c r="F87" s="6" t="str">
+        <x:v>2017-08</x:v>
+      </x:c>
+      <x:c r="G87" s="6" t="str"/>
+      <x:c r="H87" s="6" t="str">
+        <x:v>德国</x:v>
+      </x:c>
+      <x:c r="I87" s="6" t="str">
+        <x:v>德国</x:v>
+      </x:c>
+      <x:c r="J87" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K87" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L87" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M87" s="7" t="str"/>
+      <x:c r="N87" s="6" t="str"/>
+      <x:c r="O87" s="6" t="str"/>
+      <x:c r="P87" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q87" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R87" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S87" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
+      <x:c r="A88" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B88" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C88" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D88" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E88" s="6" t="str"/>
+      <x:c r="F88" s="6" t="str"/>
+      <x:c r="G88" s="6" t="str"/>
+      <x:c r="H88" s="6" t="str"/>
+      <x:c r="I88" s="6" t="str"/>
+      <x:c r="J88" s="6" t="str"/>
+      <x:c r="K88" s="6" t="str"/>
+      <x:c r="L88" s="6" t="str"/>
+      <x:c r="M88" s="7" t="str"/>
+      <x:c r="N88" s="6" t="str"/>
+      <x:c r="O88" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P88" s="6" t="str"/>
+      <x:c r="Q88" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R88" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S88" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
+      <x:c r="A89" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B89" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C89" s="6" t="str">
+        <x:v>模拟集成电路设计</x:v>
+      </x:c>
+      <x:c r="D89" s="6" t="str">
+        <x:v>华为海思无线射频部</x:v>
+      </x:c>
+      <x:c r="E89" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F89" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="G89" s="6" t="str"/>
+      <x:c r="H89" s="6" t="str"/>
+      <x:c r="I89" s="6" t="str"/>
+      <x:c r="J89" s="6" t="str"/>
+      <x:c r="K89" s="6" t="str"/>
+      <x:c r="L89" s="6" t="str"/>
+      <x:c r="M89" s="7" t="str"/>
+      <x:c r="N89" s="6" t="str"/>
+      <x:c r="O89" s="6" t="str">
+        <x:v>2019毕业后任职，2020.08加入交大，未明确离职月。</x:v>
+      </x:c>
+      <x:c r="P89" s="6" t="str"/>
+      <x:c r="Q89" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R89" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S89" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="64" customHeight="1">
+      <x:c r="A90" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B90" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C90" s="6" t="str">
+        <x:v>任教，历任教轨助理教授/教轨副教授/长聘副教授/教授</x:v>
+      </x:c>
+      <x:c r="D90" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E90" s="6" t="str">
+        <x:v>2020-08</x:v>
+      </x:c>
+      <x:c r="F90" s="6" t="str"/>
+      <x:c r="G90" s="6" t="str"/>
+      <x:c r="H90" s="6" t="str"/>
+      <x:c r="I90" s="6" t="str"/>
+      <x:c r="J90" s="6" t="str"/>
+      <x:c r="K90" s="6" t="str"/>
+      <x:c r="L90" s="6" t="str"/>
+      <x:c r="M90" s="7" t="str"/>
+      <x:c r="N90" s="6" t="str"/>
+      <x:c r="O90" s="6" t="str">
+        <x:v>各职级起讫未披露，不把2020.08自动作为教授聘任。</x:v>
+      </x:c>
+      <x:c r="P90" s="6" t="str"/>
+      <x:c r="Q90" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="R90" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S90" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="64" customHeight="1">
+      <x:c r="A91" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B91" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C91" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D91" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E91" s="6" t="str">
+        <x:v>2007-09</x:v>
+      </x:c>
+      <x:c r="F91" s="6" t="str">
+        <x:v>2011-07</x:v>
+      </x:c>
+      <x:c r="G91" s="6" t="str"/>
+      <x:c r="H91" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I91" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J91" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K91" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L91" s="6" t="str"/>
+      <x:c r="M91" s="7" t="str"/>
+      <x:c r="N91" s="6" t="str"/>
+      <x:c r="O91" s="6" t="str">
+        <x:v>官方学习经历以学位标签列示，尚未取得另行明确获授表述；保留学历阶段及学习时间，不将其计为已确证授位。</x:v>
+      </x:c>
+      <x:c r="P91" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q91" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R91" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S91" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="64" customHeight="1">
+      <x:c r="A92" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B92" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C92" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D92" s="6" t="str">
+        <x:v>北京大学</x:v>
+      </x:c>
+      <x:c r="E92" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="F92" s="6" t="str">
+        <x:v>2016-07</x:v>
+      </x:c>
+      <x:c r="G92" s="6" t="str"/>
+      <x:c r="H92" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I92" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J92" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K92" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L92" s="6" t="str"/>
+      <x:c r="M92" s="7" t="str"/>
+      <x:c r="N92" s="6" t="str"/>
+      <x:c r="O92" s="6" t="str">
+        <x:v>官方学习经历以学位标签列示，尚未取得另行明确获授表述；保留学历阶段及学习时间，不将其计为已确证授位。</x:v>
+      </x:c>
+      <x:c r="P92" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q92" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R92" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S92" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="64" customHeight="1">
+      <x:c r="A93" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B93" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C93" s="6" t="str"/>
+      <x:c r="D93" s="6" t="str">
+        <x:v>鲁汶大学/欧洲微电子中心</x:v>
+      </x:c>
+      <x:c r="E93" s="6" t="str">
+        <x:v>2019-02</x:v>
+      </x:c>
+      <x:c r="F93" s="6" t="str">
+        <x:v>2019-05</x:v>
+      </x:c>
+      <x:c r="G93" s="6" t="str"/>
+      <x:c r="H93" s="6" t="str">
+        <x:v>比利时</x:v>
+      </x:c>
+      <x:c r="I93" s="6" t="str">
+        <x:v>比利时</x:v>
+      </x:c>
+      <x:c r="J93" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K93" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L93" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M93" s="7" t="str"/>
+      <x:c r="N93" s="6" t="str"/>
+      <x:c r="O93" s="6" t="str">
+        <x:v>原文IMEC写IEMC，保留机构并列，不拆两次访问。</x:v>
+      </x:c>
+      <x:c r="P93" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q93" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R93" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S93" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="64" customHeight="1">
+      <x:c r="A94" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B94" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C94" s="6" t="str">
+        <x:v>长聘教轨副教授</x:v>
+      </x:c>
+      <x:c r="D94" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E94" s="6" t="str"/>
+      <x:c r="F94" s="6" t="str"/>
+      <x:c r="G94" s="6" t="str"/>
+      <x:c r="H94" s="6" t="str"/>
+      <x:c r="I94" s="6" t="str"/>
+      <x:c r="J94" s="6" t="str"/>
+      <x:c r="K94" s="6" t="str"/>
+      <x:c r="L94" s="6" t="str"/>
+      <x:c r="M94" s="7" t="str"/>
+      <x:c r="N94" s="6" t="str"/>
+      <x:c r="O94" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P94" s="6" t="str"/>
+      <x:c r="Q94" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="R94" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S94" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="64" customHeight="1">
+      <x:c r="A95" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B95" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C95" s="6" t="str">
+        <x:v>主任工程师、可靠性设计团队主管</x:v>
+      </x:c>
+      <x:c r="D95" s="6" t="str">
+        <x:v>上海海思技术有限公司</x:v>
+      </x:c>
+      <x:c r="E95" s="6" t="str">
+        <x:v>2017-01</x:v>
+      </x:c>
+      <x:c r="F95" s="6" t="str">
+        <x:v>2021-01</x:v>
+      </x:c>
+      <x:c r="G95" s="6" t="str"/>
+      <x:c r="H95" s="6" t="str"/>
+      <x:c r="I95" s="6" t="str"/>
+      <x:c r="J95" s="6" t="str"/>
+      <x:c r="K95" s="6" t="str"/>
+      <x:c r="L95" s="6" t="str"/>
+      <x:c r="M95" s="7" t="str"/>
+      <x:c r="N95" s="6" t="str"/>
+      <x:c r="O95" s="6" t="str"/>
+      <x:c r="P95" s="6" t="str"/>
+      <x:c r="Q95" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R95" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S95" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="64" customHeight="1">
+      <x:c r="A96" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B96" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C96" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D96" s="6" t="str">
+        <x:v>鲁汶大学/欧洲微电子中心</x:v>
+      </x:c>
+      <x:c r="E96" s="6" t="str">
+        <x:v>2019-02</x:v>
+      </x:c>
+      <x:c r="F96" s="6" t="str">
+        <x:v>2019-05</x:v>
+      </x:c>
+      <x:c r="G96" s="6" t="str"/>
+      <x:c r="H96" s="6" t="str"/>
+      <x:c r="I96" s="6" t="str"/>
+      <x:c r="J96" s="6" t="str"/>
+      <x:c r="K96" s="6" t="str"/>
+      <x:c r="L96" s="6" t="str"/>
+      <x:c r="M96" s="7" t="str"/>
+      <x:c r="N96" s="6" t="str"/>
+      <x:c r="O96" s="6" t="str"/>
+      <x:c r="P96" s="6" t="str"/>
+      <x:c r="Q96" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R96" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S96" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="64" customHeight="1">
+      <x:c r="A97" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B97" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C97" s="6" t="str">
+        <x:v>长聘教轨副教授</x:v>
+      </x:c>
+      <x:c r="D97" s="6" t="str">
+        <x:v>上海交通大学集成电路学院</x:v>
+      </x:c>
+      <x:c r="E97" s="6" t="str">
+        <x:v>2021-02</x:v>
+      </x:c>
+      <x:c r="F97" s="6" t="str"/>
+      <x:c r="G97" s="6" t="str"/>
+      <x:c r="H97" s="6" t="str"/>
+      <x:c r="I97" s="6" t="str"/>
+      <x:c r="J97" s="6" t="str"/>
+      <x:c r="K97" s="6" t="str"/>
+      <x:c r="L97" s="6" t="str"/>
+      <x:c r="M97" s="7" t="str"/>
+      <x:c r="N97" s="6" t="str"/>
+      <x:c r="O97" s="6" t="str"/>
+      <x:c r="P97" s="6" t="str"/>
+      <x:c r="Q97" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="R97" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S97" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="64" customHeight="1">
+      <x:c r="A98" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B98" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C98" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D98" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E98" s="6" t="str">
+        <x:v>1995-09</x:v>
+      </x:c>
+      <x:c r="F98" s="6" t="str">
+        <x:v>1999-07</x:v>
+      </x:c>
+      <x:c r="G98" s="6" t="str">
+        <x:v>Electrical Chemistry</x:v>
+      </x:c>
+      <x:c r="H98" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I98" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J98" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K98" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L98" s="6" t="str"/>
+      <x:c r="M98" s="7" t="str"/>
+      <x:c r="N98" s="6" t="str"/>
+      <x:c r="O98" s="6" t="str">
+        <x:v>旧学院英文教育区间为学位标签，未明言received，本批保守授位待核。</x:v>
+      </x:c>
+      <x:c r="P98" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q98" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R98" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S98" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="64" customHeight="1">
+      <x:c r="A99" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B99" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C99" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D99" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E99" s="6" t="str">
+        <x:v>2002-09</x:v>
+      </x:c>
+      <x:c r="F99" s="6" t="str">
+        <x:v>2004-07</x:v>
+      </x:c>
+      <x:c r="G99" s="6" t="str">
+        <x:v>Computer Science and Technology</x:v>
+      </x:c>
+      <x:c r="H99" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I99" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J99" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K99" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L99" s="6" t="str"/>
+      <x:c r="M99" s="7" t="str"/>
+      <x:c r="N99" s="6" t="str"/>
+      <x:c r="O99" s="6" t="str">
+        <x:v>旧学院英文教育区间为学位标签，未明言received，本批保守授位待核。</x:v>
+      </x:c>
+      <x:c r="P99" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q99" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R99" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S99" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="64" customHeight="1">
+      <x:c r="A100" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B100" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C100" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D100" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E100" s="6" t="str">
+        <x:v>2004-09</x:v>
+      </x:c>
+      <x:c r="F100" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="G100" s="6" t="str">
+        <x:v>Microelectronics and Solid State Electronics</x:v>
+      </x:c>
+      <x:c r="H100" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I100" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J100" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K100" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L100" s="6" t="str"/>
+      <x:c r="M100" s="7" t="str"/>
+      <x:c r="N100" s="6" t="str"/>
+      <x:c r="O100" s="6" t="str">
+        <x:v>旧学院英文教育区间为学位标签，未明言received，本批保守授位待核。</x:v>
+      </x:c>
+      <x:c r="P100" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q100" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R100" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S100" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="64" customHeight="1">
+      <x:c r="A101" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B101" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C101" s="6" t="str"/>
+      <x:c r="D101" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+      <x:c r="E101" s="6" t="str">
+        <x:v>2009-11</x:v>
+      </x:c>
+      <x:c r="F101" s="6" t="str">
+        <x:v>2012-02</x:v>
+      </x:c>
+      <x:c r="G101" s="6" t="str"/>
+      <x:c r="H101" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I101" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J101" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K101" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L101" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M101" s="7" t="str"/>
+      <x:c r="N101" s="6" t="str"/>
+      <x:c r="O101" s="6" t="str"/>
+      <x:c r="P101" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q101" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R101" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S101" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="64" customHeight="1">
+      <x:c r="A102" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B102" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C102" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D102" s="6" t="str">
+        <x:v>上海交通大学集成电路学院（信息与电子工程学院）</x:v>
+      </x:c>
+      <x:c r="E102" s="6" t="str"/>
+      <x:c r="F102" s="6" t="str"/>
+      <x:c r="G102" s="6" t="str"/>
+      <x:c r="H102" s="6" t="str"/>
+      <x:c r="I102" s="6" t="str"/>
+      <x:c r="J102" s="6" t="str"/>
+      <x:c r="K102" s="6" t="str"/>
+      <x:c r="L102" s="6" t="str"/>
+      <x:c r="M102" s="7" t="str"/>
+      <x:c r="N102" s="6" t="str"/>
+      <x:c r="O102" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P102" s="6" t="str"/>
+      <x:c r="Q102" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="R102" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S102" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="64" customHeight="1">
+      <x:c r="A103" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B103" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C103" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D103" s="6" t="str">
+        <x:v>上海交通大学微电子学院</x:v>
+      </x:c>
+      <x:c r="E103" s="6" t="str">
+        <x:v>2009-11</x:v>
+      </x:c>
+      <x:c r="F103" s="6" t="str">
+        <x:v>2012-02</x:v>
+      </x:c>
+      <x:c r="G103" s="6" t="str"/>
+      <x:c r="H103" s="6" t="str"/>
+      <x:c r="I103" s="6" t="str"/>
+      <x:c r="J103" s="6" t="str"/>
+      <x:c r="K103" s="6" t="str"/>
+      <x:c r="L103" s="6" t="str"/>
+      <x:c r="M103" s="7" t="str"/>
+      <x:c r="N103" s="6" t="str"/>
+      <x:c r="O103" s="6" t="str"/>
+      <x:c r="P103" s="6" t="str"/>
+      <x:c r="Q103" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R103" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S103" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="64" customHeight="1">
+      <x:c r="A104" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B104" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C104" s="6" t="str">
+        <x:v>Research Assistant Professor</x:v>
+      </x:c>
+      <x:c r="D104" s="6" t="str">
+        <x:v>上海交通大学微纳电子学系</x:v>
+      </x:c>
+      <x:c r="E104" s="6" t="str">
+        <x:v>2012-02</x:v>
+      </x:c>
+      <x:c r="F104" s="6" t="str"/>
+      <x:c r="G104" s="6" t="str"/>
+      <x:c r="H104" s="6" t="str"/>
+      <x:c r="I104" s="6" t="str"/>
+      <x:c r="J104" s="6" t="str"/>
+      <x:c r="K104" s="6" t="str"/>
+      <x:c r="L104" s="6" t="str"/>
+      <x:c r="M104" s="7" t="str"/>
+      <x:c r="N104" s="6" t="str"/>
+      <x:c r="O104" s="6" t="str">
+        <x:v>旧页历史职称，当前新学院页副研究员，不延续旧职称为现职。</x:v>
+      </x:c>
+      <x:c r="P104" s="6" t="str"/>
+      <x:c r="Q104" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="R104" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="S104" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b922592e56e4187"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdce4ccb03a3447d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3160,7 +5923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd212156ff7534b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd55bbb25fde94a77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4283,10 +7046,514 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>金晶</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>A 16/32 Gbps Dual-Mode SerDes Transmitter with Linearity Enhanced SST Driver</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>10.1587/transfun.2021KEP0006</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="str">
+        <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
+      </x:c>
+      <x:c r="H32" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
+      </x:c>
+      <x:c r="I32" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J32" s="6" t="str"/>
+      <x:c r="K32" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>景乃锋</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>A gain reconfigurable time difference amplifier with self-adaptive linearity control</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>10.1007/s10470-020-01739-1</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="str">
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
+      </x:c>
+      <x:c r="H33" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jingnaifeng.html</x:v>
+      </x:c>
+      <x:c r="I33" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J33" s="6" t="str"/>
+      <x:c r="K33" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L33" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>A 10 GHz Up-conversion Mixer with 14.5 dBm OIP3 Using Regulator-based Constant Gm Stage and Harmonic Nulling</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str"/>
+      <x:c r="E34" s="6" t="str">
+        <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="str">
+        <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
+      </x:c>
+      <x:c r="H34" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="I34" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J34" s="6" t="str">
+        <x:v>官方大会手册印刷48页/阅读器50页；正文章节用Linearized Gm，竞赛表用Constant Gm，此处保留竞赛表题名，不虚填DOI。</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L34" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>Ultrafast Large-Scale Chemical Sensing With CMOS ISFETs: A Level-Crossing Time-Domain Approach</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str"/>
+      <x:c r="E35" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="I35" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J35" s="6" t="str">
+        <x:v>学院精选书目，未逐篇核出版链接。</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L35" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>On-Probe Neural Interface ASIC for Combined Electrical Recording and optogenetic Stimulation</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str"/>
+      <x:c r="E36" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="I36" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J36" s="6" t="str">
+        <x:v>学院精选书目，未逐篇核出版链接。</x:v>
+      </x:c>
+      <x:c r="K36" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L36" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>Event-driven processing for hardware-efficient neural spike sorting</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str"/>
+      <x:c r="E37" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="H37" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="I37" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J37" s="6" t="str">
+        <x:v>学院精选书目，未逐篇核出版链接。</x:v>
+      </x:c>
+      <x:c r="K37" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L37" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>A 76.6dB-SNDR 50MHz-BW 29.2mW Noise Coupling Assisted CT Sturdy MASH ΔΣ Modulator with 1.5b/4b Quantizers in 28nm CMOS</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str"/>
+      <x:c r="E38" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="I38" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J38" s="6" t="str">
+        <x:v>学院精选书目；澳门作者PDF当前503，未声称读取全文。</x:v>
+      </x:c>
+      <x:c r="K38" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L38" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>A 76.6dB-SNDR 50MHz-BW 29.2mW Multibit CT Sturdy MASH ΔΣ Modulator with DAC Non-linearity Tolerance</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str"/>
+      <x:c r="E39" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="I39" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J39" s="6" t="str">
+        <x:v>学院精选书目；澳门作者PDF当前503，未声称读取全文。</x:v>
+      </x:c>
+      <x:c r="K39" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L39" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>Comprehensive Understanding of Flicker Noise in Advanced FinFET Technology: from Noise Sources Separation to Physical-based Modeling</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str"/>
+      <x:c r="E40" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="I40" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J40" s="6" t="str">
+        <x:v>学院精选书目，未逐篇补DOI。</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L40" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>Fast Aging-Aware Timing Analysis Framework With Temporal-Spatial Graph Neural Network</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str"/>
+      <x:c r="E41" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="H41" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="I41" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J41" s="6" t="str">
+        <x:v>学院精选书目，未逐篇补DOI。</x:v>
+      </x:c>
+      <x:c r="K41" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L41" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>A Simple Method for Series Resistance Extraction in Ultrascaled FinFETs Using Flicker Noise</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str"/>
+      <x:c r="E42" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="I42" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J42" s="6" t="str">
+        <x:v>学院精选书目，未逐篇补DOI。</x:v>
+      </x:c>
+      <x:c r="K42" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L42" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>A static-placement, dynamic-issue framework for CGRA loop accelerator</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str"/>
+      <x:c r="E43" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="H43" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="I43" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J43" s="6" t="str">
+        <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L43" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>Parallel SER analysis for combinational and sequential standard cell circuits</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str"/>
+      <x:c r="E44" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="I44" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J44" s="6" t="str">
+        <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L44" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>Soft error optimization of standard cell circuits based on gate sizing and multi-objective genetic algorithm</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str"/>
+      <x:c r="E45" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="H45" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="I45" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J45" s="6" t="str">
+        <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
+      </x:c>
+      <x:c r="K45" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="L45" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701587f6528641f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref8b59522cac402d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5134,16 +8401,16 @@
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="6" t="str">
-        <x:v>陈海宝</x:v>
+        <x:v>金晶</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>jinjing-source-1</x:v>
       </x:c>
       <x:c r="C37" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E37" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5157,16 +8424,16 @@
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
       <x:c r="A38" s="6" t="str">
-        <x:v>郭衍束</x:v>
+        <x:v>金晶</x:v>
       </x:c>
       <x:c r="B38" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>jinjing-source-2</x:v>
       </x:c>
       <x:c r="C38" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
       </x:c>
       <x:c r="D38" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E38" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5180,16 +8447,16 @@
     </x:row>
     <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="6" t="str">
-        <x:v>何卫锋</x:v>
+        <x:v>金晶</x:v>
       </x:c>
       <x:c r="B39" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>jinjing-source-3</x:v>
       </x:c>
       <x:c r="C39" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://faculty.sjtu.edu.cn/jinjing1/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_profile_local_http200_read</x:v>
       </x:c>
       <x:c r="E39" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5203,16 +8470,16 @@
     </x:row>
     <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="6" t="str">
-        <x:v>贺光辉</x:v>
+        <x:v>金晶</x:v>
       </x:c>
       <x:c r="B40" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>jinjing-source-4</x:v>
       </x:c>
       <x:c r="C40" s="6" t="str">
-        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+        <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
       </x:c>
       <x:c r="D40" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>publisher_pdf_local_http200_read</x:v>
       </x:c>
       <x:c r="E40" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5226,16 +8493,16 @@
     </x:row>
     <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="6" t="str">
-        <x:v>贺光辉</x:v>
+        <x:v>景乃锋</x:v>
       </x:c>
       <x:c r="B41" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>jingnaifeng-source-1</x:v>
       </x:c>
       <x:c r="C41" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
       </x:c>
       <x:c r="D41" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E41" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5249,16 +8516,16 @@
     </x:row>
     <x:row r="42" ht="64" customHeight="1">
       <x:c r="A42" s="6" t="str">
-        <x:v>纪志罡</x:v>
+        <x:v>景乃锋</x:v>
       </x:c>
       <x:c r="B42" s="6" t="str">
-        <x:v>institution-classification-7</x:v>
+        <x:v>jingnaifeng-source-2</x:v>
       </x:c>
       <x:c r="C42" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jingnaifeng.html</x:v>
       </x:c>
       <x:c r="D42" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E42" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5272,16 +8539,16 @@
     </x:row>
     <x:row r="43" ht="64" customHeight="1">
       <x:c r="A43" s="6" t="str">
-        <x:v>姜红兰</x:v>
+        <x:v>景乃锋</x:v>
       </x:c>
       <x:c r="B43" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>jingnaifeng-source-3</x:v>
       </x:c>
       <x:c r="C43" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
       </x:c>
       <x:c r="D43" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_author_hosted_publisher_pdf_local200</x:v>
       </x:c>
       <x:c r="E43" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -5295,31 +8562,859 @@
     </x:row>
     <x:row r="44" ht="64" customHeight="1">
       <x:c r="A44" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>lijinbo-source-1</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>lijinbo-source-2</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>lijinbo-source-3</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>https://irvingthofoundation.github.io/fellow-biographies-sobi2Task=sobi2Details&amp;sobi2Id=55.htm</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>scholarship_foundation_fellow_biography_direct_read</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>lijinbo-source-4</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>https://www.ece.ucdavis.edu/hsics/jane-gu/</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>lijinbo-source-5</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>liyongfu-source-1</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>liyongfu-source-2</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liyongfu.html</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>liyongfu-source-3</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>https://bicasl.sjtu.edu.cn/info/1017/1079.htm</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F51" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>李永福</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>liyongfu-source-4</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>https://yongfu-li.github.io/biography.html</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>official_lab_linked_personal_biography_direct_local200</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F52" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>liuyan-source-1</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F53" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>liuyan-source-2</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>liuyan-source-3</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>https://profiles.imperial.ac.uk/yan.liu06</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>liuyan-source-4</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>https://www.imperial.ac.uk/media/imperial-college/research-centres-and-groups/centre-for-bio-inspired-technology/CBIT_Annual_Report_2011.pdf</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>official_search_index_only</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F56" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G56" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>maozhigang-source-1</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>maozhigang-source-2</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/maozhigang.html</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>maozhigang-source-3</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>https://faculty.sjtu.edu.cn/maozhigang</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>official_search_index_only</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>qiliang-source-1</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F60" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>qiliang-source-2</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>祁亮</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>qiliang-source-3</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>https://rto.um.edu.mo/wp-content/uploads/cv/RuiMartins_cv_details.pdf</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>official_search_index_only</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F62" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>renpengpeng-source-1</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F63" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>renpengpeng-source-2</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F64" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G64" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>任鹏鹏</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
+        <x:v>renpengpeng-source-3</x:v>
+      </x:c>
+      <x:c r="C65" s="6" t="str">
+        <x:v>https://lemon.sjtu.edu.cn/team/</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F65" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>shengweiguang-source-1</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml.html</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F66" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G66" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>shengweiguang-source-2</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
+      </x:c>
+      <x:c r="D67" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F67" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G67" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>shengweiguang-source-3</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str">
+        <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
+      </x:c>
+      <x:c r="D68" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="6" t="str">
+        <x:v>陈海宝</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C69" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D69" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F69" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G69" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="6" t="str">
+        <x:v>郭衍束</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C70" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D70" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F70" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="6" t="str">
+        <x:v>何卫锋</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C71" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D71" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F71" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="64" customHeight="1">
+      <x:c r="A72" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B72" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C72" s="6" t="str">
+        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+      </x:c>
+      <x:c r="D72" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F72" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G72" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
+      <x:c r="A73" s="6" t="str">
+        <x:v>贺光辉</x:v>
+      </x:c>
+      <x:c r="B73" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C73" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D73" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F73" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G73" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
+      <x:c r="A74" s="6" t="str">
+        <x:v>纪志罡</x:v>
+      </x:c>
+      <x:c r="B74" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C74" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D74" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E74" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F74" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G74" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
+      <x:c r="A75" s="6" t="str">
+        <x:v>姜红兰</x:v>
+      </x:c>
+      <x:c r="B75" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D75" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E75" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F75" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G75" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
+      <x:c r="A76" s="6" t="str">
         <x:v>蒋剑飞</x:v>
       </x:c>
-      <x:c r="B44" s="6" t="str">
+      <x:c r="B76" s="6" t="str">
         <x:v>institution-classification-3</x:v>
       </x:c>
-      <x:c r="C44" s="6" t="str">
+      <x:c r="C76" s="6" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
       </x:c>
-      <x:c r="D44" s="6" t="str">
+      <x:c r="D76" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E44" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F44" s="6" t="str">
-        <x:v>sjtu</x:v>
-      </x:c>
-      <x:c r="G44" s="6" t="str">
+      <x:c r="E76" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F76" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G76" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
+      <x:c r="A77" s="6" t="str">
+        <x:v>李金波</x:v>
+      </x:c>
+      <x:c r="B77" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C77" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D77" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E77" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F77" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G77" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
+      <x:c r="A78" s="6" t="str">
+        <x:v>刘彦</x:v>
+      </x:c>
+      <x:c r="B78" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C78" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D78" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E78" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F78" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G78" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="64" customHeight="1">
+      <x:c r="A79" s="6" t="str">
+        <x:v>毛志刚</x:v>
+      </x:c>
+      <x:c r="B79" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C79" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D79" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E79" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F79" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G79" s="6" t="str">
+        <x:v>上海交通大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64" customHeight="1">
+      <x:c r="A80" s="6" t="str">
+        <x:v>绳伟光</x:v>
+      </x:c>
+      <x:c r="B80" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C80" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D80" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E80" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F80" s="6" t="str">
+        <x:v>sjtu</x:v>
+      </x:c>
+      <x:c r="G80" s="6" t="str">
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b7092afe4634f12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89d11729e1fb40e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R790ef1d19bd649eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R498a7d4502784c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R13d33f438ee744e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R0bd985b136ce4b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rd4742dbe411b4139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2f336a9600464708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rdbb851884beb4f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R33ea4218095c4eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc22b137bafae42b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rd77acd8ea3d44c22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T8_0" displayName="T8_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T11_0" displayName="T11_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T8_1" displayName="T8_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T11_1" displayName="T11_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T8_2" displayName="T8_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T11_2" displayName="T11_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T8_3" displayName="T8_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T11_3" displayName="T11_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T8_4" displayName="T8_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T11_4" displayName="T11_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -1112,7 +1112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4dcd7d1bfac4c1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43bdd92df83a4746"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5785,7 +5785,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdce4ccb03a3447d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33c8273a2c4e4b12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5923,7 +5923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd55bbb25fde94a77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c424a95431f42f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5999,7 +5999,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
@@ -6008,7 +6008,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str"/>
       <x:c r="K2" s="6" t="str">
@@ -6033,7 +6033,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
@@ -6042,7 +6042,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str"/>
       <x:c r="K3" s="6" t="str">
@@ -6067,7 +6067,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
@@ -6076,7 +6076,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chencheng.html</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str"/>
       <x:c r="K4" s="6" t="str">
@@ -6101,7 +6101,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
@@ -6110,7 +6110,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="I5" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str">
         <x:v>官网精选书目；未独立验证出版者单篇页面。</x:v>
@@ -6137,7 +6137,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
@@ -6146,7 +6146,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
         <x:v>官网精选书目；未独立验证出版者单篇页面。</x:v>
@@ -6173,7 +6173,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
@@ -6182,7 +6182,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/chenhaibao.html</x:v>
       </x:c>
       <x:c r="I7" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
         <x:v>官网精选书目；未独立验证出版者单篇页面。</x:v>
@@ -6209,7 +6209,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
@@ -6218,7 +6218,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J8" s="6" t="str"/>
       <x:c r="K8" s="6" t="str">
@@ -6243,7 +6243,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
@@ -6252,7 +6252,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str"/>
       <x:c r="K9" s="6" t="str">
@@ -6277,7 +6277,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
@@ -6286,7 +6286,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/fuyuzhuo.html</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str"/>
       <x:c r="K10" s="6" t="str">
@@ -6311,7 +6311,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
@@ -6320,7 +6320,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J11" s="6" t="str">
         <x:v>官网书目原样标题；第一项Buk疑拼写但未擅改。</x:v>
@@ -6347,7 +6347,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
@@ -6356,7 +6356,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
         <x:v>官网书目原样标题；第一项Buk疑拼写但未擅改。</x:v>
@@ -6385,7 +6385,7 @@
         <x:v>https://doi.org/10.1109/JSSC.2025.3589101</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
@@ -6394,7 +6394,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/3079.html</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
-        <x:v>doi_explicitly_listed_on_official_profile</x:v>
+        <x:v>DOI由官方个人页明确列示，未据此声称出版社落地页或全文已读。；doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str">
         <x:v>官网书目原样标题；第一项Buk疑拼写但未擅改。</x:v>
@@ -6419,7 +6419,7 @@
         <x:v>https://www.gs.sjtu.edu.cn/post/detail/Z3MzNDk</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>doctoral_dissertation</x:v>
+        <x:v>博士学位论文记录；doctoral_dissertation</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>https://www.gs.sjtu.edu.cn/post/detail/Z3MzNDk</x:v>
@@ -6428,7 +6428,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
-        <x:v>official_dissertation_award_table_not_full_text</x:v>
+        <x:v>官方学位论文评选名单记录，非论文全文；提名年份不是授位年份。；official_dissertation_award_table_not_full_text</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str">
         <x:v>官方2023获提名，不把评奖年当论文完成或授位年。</x:v>
@@ -6455,7 +6455,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
@@ -6464,7 +6464,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J15" s="6" t="str"/>
       <x:c r="K15" s="6" t="str">
@@ -6489,7 +6489,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
@@ -6498,7 +6498,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/guoyuekang.html</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J16" s="6" t="str"/>
       <x:c r="K16" s="6" t="str">
@@ -6523,7 +6523,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
@@ -6532,7 +6532,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J17" s="6" t="str"/>
       <x:c r="K17" s="6" t="str">
@@ -6557,7 +6557,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
@@ -6566,7 +6566,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J18" s="6" t="str"/>
       <x:c r="K18" s="6" t="str">
@@ -6593,7 +6593,7 @@
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>journal_manuscript</x:v>
+        <x:v>期刊论文作者稿（非已核最终出版版）；journal_manuscript</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
@@ -6602,7 +6602,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heweifeng.html</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str">
-        <x:v>primary_full_text_read</x:v>
+        <x:v>本条原始作者稿或单篇正文已读；只发布精选书目，不发布全文。；primary_full_text_read</x:v>
       </x:c>
       <x:c r="J19" s="6" t="str">
         <x:v>已读2024作者接受稿，首页标明accepted for publication与DOI；2024指该稿版本，不据此断言最终卷期年份。</x:v>
@@ -6629,7 +6629,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
@@ -6638,7 +6638,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J20" s="6" t="str"/>
       <x:c r="K20" s="6" t="str">
@@ -6663,7 +6663,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
       </x:c>
       <x:c r="F21" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
@@ -6672,7 +6672,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J21" s="6" t="str"/>
       <x:c r="K21" s="6" t="str">
@@ -6699,7 +6699,7 @@
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
-        <x:v>journal_manuscript</x:v>
+        <x:v>期刊论文作者稿（非已核最终出版版）；journal_manuscript</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/f10d9bfa-80d4-490a-b828-1d256a49e42a.pdf</x:v>
@@ -6708,7 +6708,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/heguanghui.html</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
-        <x:v>primary_full_text_read</x:v>
+        <x:v>本条原始作者稿或单篇正文已读；只发布精选书目，不发布全文。；primary_full_text_read</x:v>
       </x:c>
       <x:c r="J22" s="6" t="str">
         <x:v>2024作者接受稿，不是最终卷期核验。</x:v>
@@ -6735,7 +6735,7 @@
         <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/</x:v>
       </x:c>
       <x:c r="F23" s="6" t="str">
-        <x:v>doctoral_thesis</x:v>
+        <x:v>博士学位论文；doctoral_thesis</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
         <x:v>https://researchonline.ljmu.ac.uk/id/eprint/5975/</x:v>
@@ -6744,7 +6744,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
-        <x:v>official_repository_record_and_thesis_read</x:v>
+        <x:v>官方学位论文仓储记录与论文已读；只发布必要书目及指导证据，不发布全文。；official_repository_record_and_thesis_read</x:v>
       </x:c>
       <x:c r="J23" s="6" t="str">
         <x:v>正式校级机构库论文记录；论文PDF已读，授位信息另依作者简历。</x:v>
@@ -6773,7 +6773,7 @@
         <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
         <x:v>https://researchonline.ljmu.ac.uk/13797/1/An_Assessment_of_the_Statistical_Distribution_of_Random_Telegraph_Noise_Time_Constants.pdf</x:v>
@@ -6782,7 +6782,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
-        <x:v>primary_full_text_read</x:v>
+        <x:v>本条原始作者稿或单篇正文已读；只发布精选书目，不发布全文。；primary_full_text_read</x:v>
       </x:c>
       <x:c r="J24" s="6" t="str">
         <x:v>机构库论文首页与末页已读，附作者本人简历。</x:v>
@@ -6809,7 +6809,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
       </x:c>
       <x:c r="F25" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
@@ -6818,7 +6818,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jizhigang.html</x:v>
       </x:c>
       <x:c r="I25" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J25" s="6" t="str"/>
       <x:c r="K25" s="6" t="str">
@@ -6843,7 +6843,7 @@
         <x:v>https://www.ece.ualberta.ca/~jhan8/publications/FINAL_VERSION_TCASI.pdf</x:v>
       </x:c>
       <x:c r="F26" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
@@ -6852,7 +6852,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
       </x:c>
       <x:c r="I26" s="6" t="str">
-        <x:v>official_list_and_author_manuscript_read</x:v>
+        <x:v>官方书目及作者稿已读，不等于所有出版社最终版本已核。；official_list_and_author_manuscript_read</x:v>
       </x:c>
       <x:c r="J26" s="6" t="str">
         <x:v>官网论文元数据与大学域名作者稿标题/作者一致；未独立核出版者全文。</x:v>
@@ -6879,7 +6879,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
       </x:c>
       <x:c r="F27" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
@@ -6888,7 +6888,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
       </x:c>
       <x:c r="I27" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J27" s="6" t="str">
         <x:v>官网列2026；卷期、页码、DOI及最终出版状态未独立核验。</x:v>
@@ -6915,7 +6915,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
       </x:c>
       <x:c r="F28" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
@@ -6924,7 +6924,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jianghonglan.html</x:v>
       </x:c>
       <x:c r="I28" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J28" s="6" t="str">
         <x:v>官网列2026；卷期、页码、DOI及最终出版状态未独立核验。</x:v>
@@ -6953,7 +6953,7 @@
         <x:v>https://ieeexplore.ieee.org/abstract/document/11488179</x:v>
       </x:c>
       <x:c r="F29" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
@@ -6962,7 +6962,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
       </x:c>
       <x:c r="I29" s="6" t="str">
-        <x:v>publisher_metadata_indexed_body_unavailable</x:v>
+        <x:v>出版者检索索引元数据可见，落地页正文不可读；不升级为已读全文。；publisher_metadata_indexed_body_unavailable</x:v>
       </x:c>
       <x:c r="J29" s="6" t="str">
         <x:v>本人官网书目确认身份；DOI与Early Access元数据来自出版者检索记录。出版者正文418后停止，不能声称全文已读。</x:v>
@@ -6989,7 +6989,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
       </x:c>
       <x:c r="F30" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
@@ -6998,7 +6998,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
       </x:c>
       <x:c r="I30" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J30" s="6" t="str">
         <x:v>仅官网精选书目；单篇出版者链接未核。</x:v>
@@ -7025,7 +7025,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
       </x:c>
       <x:c r="F31" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
@@ -7034,7 +7034,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jiangjianfei.html</x:v>
       </x:c>
       <x:c r="I31" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J31" s="6" t="str">
         <x:v>仅官网精选书目；单篇出版者链接未核。</x:v>
@@ -7063,7 +7063,7 @@
         <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
       </x:c>
       <x:c r="F32" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
         <x:v>https://www.jstage.jst.go.jp/article/transfun/E105.A/11/E105.A_2021KEP0006/_pdf</x:v>
@@ -7072,7 +7072,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jinjing.html</x:v>
       </x:c>
       <x:c r="I32" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J32" s="6" t="str"/>
       <x:c r="K32" s="6" t="str">
@@ -7099,7 +7099,7 @@
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
       </x:c>
       <x:c r="F33" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
         <x:v>https://dai.sjtu.edu.cn/my_file/pdf/d8d38131-ad2c-4455-9050-3f31bf017f1a.pdf</x:v>
@@ -7108,7 +7108,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/jingnaifeng.html</x:v>
       </x:c>
       <x:c r="I33" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J33" s="6" t="str"/>
       <x:c r="K33" s="6" t="str">
@@ -7133,7 +7133,7 @@
         <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
       </x:c>
       <x:c r="F34" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
         <x:v>https://2018.ims-ieee.org/sites/default/files/content_images/098-003%20IMS%202018%20Program%20Book-ForWeb.pdf</x:v>
@@ -7142,7 +7142,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/2765.html</x:v>
       </x:c>
       <x:c r="I34" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J34" s="6" t="str">
         <x:v>官方大会手册印刷48页/阅读器50页；正文章节用Linearized Gm，竞赛表用Constant Gm，此处保留竞赛表题名，不虚填DOI。</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="F35" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
@@ -7178,7 +7178,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="I35" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J35" s="6" t="str">
         <x:v>学院精选书目，未逐篇核出版链接。</x:v>
@@ -7205,7 +7205,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="F36" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
@@ -7214,7 +7214,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="I36" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J36" s="6" t="str">
         <x:v>学院精选书目，未逐篇核出版链接。</x:v>
@@ -7241,7 +7241,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="F37" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
@@ -7250,7 +7250,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/liuyan.html</x:v>
       </x:c>
       <x:c r="I37" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J37" s="6" t="str">
         <x:v>学院精选书目，未逐篇核出版链接。</x:v>
@@ -7277,7 +7277,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
       </x:c>
       <x:c r="F38" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G38" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
@@ -7286,7 +7286,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
       </x:c>
       <x:c r="I38" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J38" s="6" t="str">
         <x:v>学院精选书目；澳门作者PDF当前503，未声称读取全文。</x:v>
@@ -7313,7 +7313,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
       </x:c>
       <x:c r="F39" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
@@ -7322,7 +7322,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/qiliang.html</x:v>
       </x:c>
       <x:c r="I39" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J39" s="6" t="str">
         <x:v>学院精选书目；澳门作者PDF当前503，未声称读取全文。</x:v>
@@ -7349,7 +7349,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="F40" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G40" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
@@ -7358,7 +7358,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="I40" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J40" s="6" t="str">
         <x:v>学院精选书目，未逐篇补DOI。</x:v>
@@ -7385,7 +7385,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="F41" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G41" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
@@ -7394,7 +7394,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="I41" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J41" s="6" t="str">
         <x:v>学院精选书目，未逐篇补DOI。</x:v>
@@ -7421,7 +7421,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="F42" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G42" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
@@ -7430,7 +7430,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/renpengpeng.html</x:v>
       </x:c>
       <x:c r="I42" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J42" s="6" t="str">
         <x:v>学院精选书目，未逐篇补DOI。</x:v>
@@ -7457,7 +7457,7 @@
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
       </x:c>
       <x:c r="F43" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G43" s="6" t="str">
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
@@ -7466,7 +7466,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
       </x:c>
       <x:c r="I43" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J43" s="6" t="str">
         <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
@@ -7493,7 +7493,7 @@
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
       </x:c>
       <x:c r="F44" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G44" s="6" t="str">
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
@@ -7502,7 +7502,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
       </x:c>
       <x:c r="I44" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J44" s="6" t="str">
         <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
@@ -7529,7 +7529,7 @@
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
       </x:c>
       <x:c r="F45" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G45" s="6" t="str">
         <x:v>https://tw.seiee.sjtu.edu.cn/english/detail/386_1252.htm</x:v>
@@ -7538,7 +7538,7 @@
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/shengweiguang.html</x:v>
       </x:c>
       <x:c r="I45" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J45" s="6" t="str">
         <x:v>旧学院官网精选书目，未逐篇出版链接。</x:v>
@@ -7553,7 +7553,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref8b59522cac402d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec613f76fffa443a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9414,7 +9414,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89d11729e1fb40e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec38dbd453eb4894"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2f336a9600464708"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rdbb851884beb4f2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R33ea4218095c4eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc22b137bafae42b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rd77acd8ea3d44c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R075722eec32d4936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R83ba680d5ef94c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rbc9919ee911243dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R5ef3c97cabf74c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R9c543ef966ff4d67"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T11_0" displayName="T11_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T43_0" displayName="T43_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T11_1" displayName="T11_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T43_1" displayName="T43_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T11_2" displayName="T11_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T43_2" displayName="T43_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T11_3" displayName="T11_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T43_3" displayName="T43_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T11_4" displayName="T11_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T43_4" displayName="T43_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -1112,7 +1112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43bdd92df83a4746"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re380d118cbb64595"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5785,7 +5785,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33c8273a2c4e4b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a58a418592945fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5866,7 +5866,7 @@
         <x:v>active_officially_listed</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>当前学院师资名单列教授，不据此推定全职人事或未来状态。</x:v>
+        <x:v>当前学院师资名单列教授，不据此推定全职人事或未来状态。；明确事件绑定；关联经历ID：["sjtu-guoyuekang-education-1"]；合述机构未单独披露；指导起止：起始时间未披露 至 结束时间未披露；2023优秀博士学位论文提名名单表头明确导师；过悦康行对应周健军，不从合著推断。</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
         <x:v>https://icisee.sjtu.edu.cn/jiaoshiml/zhoujianjun.html</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>official_profile_indexed_current_role</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>东南大学现行官方主页检索内容列首席教授；会议主办方公开检索履历称2025年加入东南大学。后续独立HTTP下载403已停止，没有原始下载正文；不声称独立人事在岗核验，退休状态未知。</x:v>
+        <x:v>东南大学现行官方主页检索内容列首席教授；会议主办方公开检索履历称2025年加入东南大学。后续独立HTTP下载403已停止，没有原始下载正文；不声称独立人事在岗核验，退休状态未知。；明确事件绑定；关联经历ID：["sjtu-jizhigang-education-3"]；合述机构未单独披露；指导起止：起始时间未披露 至 结束时间未披露；直接supervisor表述。全名连接由同机构同领域作者简介、学校中文学术履历和官方会议英文简历交叉核对；Dr. Wei仅获普通感谢，不升级第二导师。 当前角色证据层级是官方页面检索内容，不是独立HTTP正文下载成功。</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str"/>
       <x:c r="I3" s="6" t="str">
@@ -5923,7 +5923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c424a95431f42f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c1e55a3f4449e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7553,7 +7553,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec613f76fffa443a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb1ce100c0149f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9414,7 +9414,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec38dbd453eb4894"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad7c22761d1a47d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R075722eec32d4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R83ba680d5ef94c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rbc9919ee911243dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R5ef3c97cabf74c8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R9c543ef966ff4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf4e2a6cf774845f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Ref07a325a3b24c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R5b4604c405814f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R1b2867712a844818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rf93540069b2441e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T43_0" displayName="T43_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T73_0" displayName="T73_0" ref="A1:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T43_1" displayName="T43_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T73_1" displayName="T73_1" ref="A1:S104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T43_2" displayName="T43_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T73_2" displayName="T73_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T43_3" displayName="T43_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T73_3" displayName="T73_3" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T43_4" displayName="T43_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T73_4" displayName="T73_4" ref="A1:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -440,7 +440,7 @@
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="110" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
@@ -548,7 +548,7 @@
         <x:v>上海交通大学</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="64" customHeight="1">
+    <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>付宇卓</x:v>
       </x:c>
@@ -568,7 +568,7 @@
         <x:v>学历机构、起讫、导师未在本轮直接官方资料取得；未采用第三方同名简历补齐。</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
-        <x:v>分批核实资料，不是完整名录</x:v>
+        <x:v>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数字集成电路设计；课程负责人；教学／课程开设时间：时间未披露；来源ID：fuyuzhuo-source-3；https://news.sjtu.edu.cn/ztzl_jdjk/20241223/205827.html</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
         <x:v>公开个人页（时效以核对日为准）</x:v>
@@ -1112,7 +1112,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re380d118cbb64595"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf3936d723b048d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5785,7 +5785,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a58a418592945fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbdecb6815a244a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5923,7 +5923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c1e55a3f4449e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R079de570c2434a90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7553,7 +7553,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb1ce100c0149f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc857422049064387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9414,7 +9414,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad7c22761d1a47d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6606e41e0ef3495c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/sjtu-ic-chipdesign.xlsx
+++ b/site/exports/sjtu-ic-chipdesign.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数字集成电路设计；课程负责人；教学／课程开设时间：时间未披露；来源ID：fuyuzhuo-source-3；https://news.sjtu.edu.cn/ztzl_jdjk/20241223/205827.html</t>
+          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数字集成电路设计；课程负责人；教学／课程开设时间：时间未披露；来源ID：fuyuzhuo-source-3；https://news.sjtu.edu.cn/ztzl_jdjk/20241223/205827.html；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -867,12 +867,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -920,12 +920,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
